--- a/Templates/MIAPPE_Spreadsheet_Template.xlsx
+++ b/Templates/MIAPPE_Spreadsheet_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\MIAPPE\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0F1FBB-81F6-4A67-A930-086AB691A5D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124BB8E1-36AC-49BF-853B-377E09B6840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="674">
   <si>
     <t>README</t>
   </si>
@@ -2246,6 +2246,12 @@
   </si>
   <si>
     <t>Other perturbation</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>S2</t>
   </si>
 </sst>
 </file>
@@ -5210,8 +5216,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:S2" insertRow="1" totalsRowShown="0" dataDxfId="91">
-  <autoFilter ref="A1:S2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:S3" totalsRowShown="0" dataDxfId="91">
+  <autoFilter ref="A1:S3" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="110"/>
     <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="109"/>
@@ -11017,6 +11023,11 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{C9CAF3F9-1E81-44B5-A4D0-E0C67AD055FB}">
+      <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
@@ -13385,6 +13396,11 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{C55DF1AA-2FC1-4B63-B809-4C8E590CBCDD}">
+      <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
@@ -17992,7 +18008,9 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="54"/>
+      <c r="A2" s="54" t="s">
+        <v>672</v>
+      </c>
       <c r="B2" s="55"/>
       <c r="C2" s="55"/>
       <c r="D2" s="54"/>
@@ -18013,25 +18031,27 @@
       <c r="S2" s="54"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="56"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
+      <c r="A3" s="54" t="s">
+        <v>673</v>
+      </c>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="54"/>
     </row>
     <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56"/>
@@ -20194,6 +20214,11 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{95E373B1-A45B-45DE-8BD8-32BF05749EFB}">
+      <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
@@ -21281,6 +21306,11 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{75CB6A25-A2F7-4AF7-A843-2FCA2B2FD86D}">
+      <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
@@ -21297,7 +21327,7 @@
   <dimension ref="A1:X997"/>
   <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.921875" customWidth="1"/>
+    <col min="1" max="1" width="11.4609375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.921875" customWidth="1"/>
     <col min="3" max="3" width="22.61328125" customWidth="1"/>
     <col min="4" max="4" width="10.765625" customWidth="1"/>
@@ -22570,6 +22600,11 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{8C59A5A3-F5F2-4F3A-B80E-7871C95E3BB2}">
+      <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
@@ -23621,6 +23656,11 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{F0012BD8-AD23-4059-8955-C8C950130C4D}">
+      <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
@@ -24800,6 +24840,11 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{42E4EFB7-2070-4231-8483-B5E1780AC7C2}">
+      <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
@@ -25954,6 +25999,11 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{649E6E49-1C43-4DBC-A22C-62A99DEF1F6A}">
+      <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">

--- a/Templates/MIAPPE_Spreadsheet_Template.xlsx
+++ b/Templates/MIAPPE_Spreadsheet_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\MIAPPE\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124BB8E1-36AC-49BF-853B-377E09B6840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A410AC2B-76C3-49BA-BF00-555A165A057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="675">
   <si>
     <t>README</t>
   </si>
@@ -2252,6 +2252,9 @@
   </si>
   <si>
     <t>S2</t>
+  </si>
+  <si>
+    <t>parentStudyId</t>
   </si>
 </sst>
 </file>
@@ -2633,7 +2636,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="130">
+  <dxfs count="131">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -5134,15 +5157,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="MiappeStyle" pivot="0" count="9" xr9:uid="{59C54380-D204-4007-9CC6-0890CCDEE3C9}">
-      <tableStyleElement type="wholeTable" dxfId="129"/>
-      <tableStyleElement type="headerRow" dxfId="128"/>
-      <tableStyleElement type="totalRow" dxfId="127"/>
-      <tableStyleElement type="firstColumn" dxfId="126"/>
-      <tableStyleElement type="lastColumn" dxfId="125"/>
-      <tableStyleElement type="firstRowStripe" dxfId="124"/>
-      <tableStyleElement type="secondRowStripe" dxfId="123"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="122"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="121"/>
+      <tableStyleElement type="wholeTable" dxfId="130"/>
+      <tableStyleElement type="headerRow" dxfId="129"/>
+      <tableStyleElement type="totalRow" dxfId="128"/>
+      <tableStyleElement type="firstColumn" dxfId="127"/>
+      <tableStyleElement type="lastColumn" dxfId="126"/>
+      <tableStyleElement type="firstRowStripe" dxfId="125"/>
+      <tableStyleElement type="secondRowStripe" dxfId="124"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="123"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="122"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5157,204 +5180,205 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}" name="investigation" displayName="investigation" ref="A1:H2" totalsRowShown="0" headerRowDxfId="111" dataDxfId="112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}" name="investigation" displayName="investigation" ref="A1:H2" totalsRowShown="0" headerRowDxfId="112" dataDxfId="113">
   <autoFilter ref="A1:H2" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{25F01F79-3E24-44AF-B5E3-4EB20FD9A360}" name="investigationId" dataDxfId="120"/>
-    <tableColumn id="2" xr3:uid="{16E59F0F-AC6D-4504-A428-E7D7AC601401}" name="investigationTitle" dataDxfId="119"/>
-    <tableColumn id="3" xr3:uid="{4668A34F-CEFF-43A7-84AA-B014E3A90F47}" name="investigationDescription" dataDxfId="118"/>
-    <tableColumn id="4" xr3:uid="{403353FA-EBA5-418F-8273-81472CDF29D4}" name="submissionDate" dataDxfId="117"/>
-    <tableColumn id="5" xr3:uid="{18E43DB3-511F-4E0E-B357-B4A6E40F0660}" name="publicReleaseDate" dataDxfId="116"/>
-    <tableColumn id="6" xr3:uid="{91C01C8C-69AF-4B74-BA16-1C962EDAF32D}" name="license" dataDxfId="115"/>
-    <tableColumn id="7" xr3:uid="{E94BB99A-781A-4442-AD9C-7E4D99028DC9}" name="miappeVersion" dataDxfId="114"/>
-    <tableColumn id="8" xr3:uid="{91B9E445-65BD-412A-95C1-EA371F946FCA}" name="associatedPublication" dataDxfId="113"/>
+    <tableColumn id="1" xr3:uid="{25F01F79-3E24-44AF-B5E3-4EB20FD9A360}" name="investigationId" dataDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{16E59F0F-AC6D-4504-A428-E7D7AC601401}" name="investigationTitle" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{4668A34F-CEFF-43A7-84AA-B014E3A90F47}" name="investigationDescription" dataDxfId="119"/>
+    <tableColumn id="4" xr3:uid="{403353FA-EBA5-418F-8273-81472CDF29D4}" name="submissionDate" dataDxfId="118"/>
+    <tableColumn id="5" xr3:uid="{18E43DB3-511F-4E0E-B357-B4A6E40F0660}" name="publicReleaseDate" dataDxfId="117"/>
+    <tableColumn id="6" xr3:uid="{91C01C8C-69AF-4B74-BA16-1C962EDAF32D}" name="license" dataDxfId="116"/>
+    <tableColumn id="7" xr3:uid="{E94BB99A-781A-4442-AD9C-7E4D99028DC9}" name="miappeVersion" dataDxfId="115"/>
+    <tableColumn id="8" xr3:uid="{91B9E445-65BD-412A-95C1-EA371F946FCA}" name="associatedPublication" dataDxfId="114"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="18" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="19" dataDxfId="20">
   <autoFilter ref="A1:G2" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{92A1E618-2F85-46E4-B7EF-76ED045C215B}" name="obsUnitId" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{A0DFEC37-340B-4DF8-907B-A9769602FD28}" name="sampleId" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{D455AF29-BE41-4DDA-A9B2-A46F4EEA6767}" name="developmentStage" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{C24109D3-E8A6-4810-A0A6-ACD6730F0D08}" name="anatomicalEntity" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{5C630D57-B424-4325-BC0C-BEEBEDC89DBB}" name="sampleDesc" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{CDEC6C64-2387-4FCF-9A2C-63F54020D0A0}" name="collectionDate" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{FFB2A4F7-3C7D-4BC5-AD9E-C14C20349305}" name="externalId" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{92A1E618-2F85-46E4-B7EF-76ED045C215B}" name="obsUnitId" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{A0DFEC37-340B-4DF8-907B-A9769602FD28}" name="sampleId" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{D455AF29-BE41-4DDA-A9B2-A46F4EEA6767}" name="developmentStage" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{C24109D3-E8A6-4810-A0A6-ACD6730F0D08}" name="anatomicalEntity" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{5C630D57-B424-4325-BC0C-BEEBEDC89DBB}" name="sampleDesc" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{CDEC6C64-2387-4FCF-9A2C-63F54020D0A0}" name="collectionDate" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{FFB2A4F7-3C7D-4BC5-AD9E-C14C20349305}" name="externalId" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:Q2" insertRow="1" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:Q2" insertRow="1" totalsRowShown="0" dataDxfId="1">
   <autoFilter ref="A1:Q2" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccNumber" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccessionNumber" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccessionNumber" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccNumber" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccNumber" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccNumber" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="timeScale" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccNumber" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccessionNumber" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccessionNumber" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccNumber" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccNumber" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccNumber" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="timeScale" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:S3" totalsRowShown="0" dataDxfId="91">
-  <autoFilter ref="A1:S3" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}"/>
-  <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="110"/>
-    <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="109"/>
-    <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="108"/>
-    <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="107"/>
-    <tableColumn id="5" xr3:uid="{E557DB42-3379-4598-AAF9-21798BC64DAB}" name="studyEndDate" dataDxfId="106"/>
-    <tableColumn id="6" xr3:uid="{1EEA2EC5-CA19-40B4-9DFB-2DE9A9E916EA}" name="contactInst" dataDxfId="105"/>
-    <tableColumn id="7" xr3:uid="{E0A5C222-CFE5-4E9C-8E84-0892043DBD21}" name="locationCountry" dataDxfId="104"/>
-    <tableColumn id="8" xr3:uid="{7B635D2A-56C5-48B0-A880-E33ADE030AB1}" name="siteName" dataDxfId="103"/>
-    <tableColumn id="9" xr3:uid="{2F8227C3-F11C-4DAA-93EB-CEBD94FF81A9}" name="locationLatitude" dataDxfId="102"/>
-    <tableColumn id="10" xr3:uid="{6A14EB46-0BF4-45C6-9048-E1B7D13E633A}" name="locationLongitude" dataDxfId="101"/>
-    <tableColumn id="11" xr3:uid="{9954429A-AA41-408C-BB04-D73EDB89D73F}" name="locationAltitude" dataDxfId="100"/>
-    <tableColumn id="12" xr3:uid="{39FEDA43-D994-4742-B319-3DFED43EF79B}" name="expeDesignDesc" dataDxfId="99"/>
-    <tableColumn id="13" xr3:uid="{C9F6A881-1CF1-4AD9-8305-B7E26FD78E3B}" name="expeDesignType" dataDxfId="98"/>
-    <tableColumn id="14" xr3:uid="{253A58C7-1A2A-4D25-9622-3AE33F89A685}" name="obsUnitLevelHierarchy" dataDxfId="97"/>
-    <tableColumn id="15" xr3:uid="{10DCEB5F-0BF5-4476-83E5-B973A516A8CD}" name="obsUnitDesc" dataDxfId="96"/>
-    <tableColumn id="16" xr3:uid="{0D36E7FE-2245-4B79-9A59-4C64590731A5}" name="growthFacilityDesc" dataDxfId="95"/>
-    <tableColumn id="17" xr3:uid="{599307E8-6E88-4D3F-BF48-ADF70D109D18}" name="growthFacilityType" dataDxfId="94"/>
-    <tableColumn id="18" xr3:uid="{63403E81-283C-4E2E-984D-9EFC0886E90C}" name="culturalPractice" dataDxfId="93"/>
-    <tableColumn id="19" xr3:uid="{E74D4B3A-67BC-482F-8485-FC7D9088A8B6}" name="expeDesignMap" dataDxfId="92"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:T3" totalsRowShown="0" dataDxfId="92">
+  <autoFilter ref="A1:T3" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}"/>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="111"/>
+    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="parentStudyId" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="109"/>
+    <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="108"/>
+    <tableColumn id="5" xr3:uid="{E557DB42-3379-4598-AAF9-21798BC64DAB}" name="studyEndDate" dataDxfId="107"/>
+    <tableColumn id="6" xr3:uid="{1EEA2EC5-CA19-40B4-9DFB-2DE9A9E916EA}" name="contactInst" dataDxfId="106"/>
+    <tableColumn id="7" xr3:uid="{E0A5C222-CFE5-4E9C-8E84-0892043DBD21}" name="locationCountry" dataDxfId="105"/>
+    <tableColumn id="8" xr3:uid="{7B635D2A-56C5-48B0-A880-E33ADE030AB1}" name="siteName" dataDxfId="104"/>
+    <tableColumn id="9" xr3:uid="{2F8227C3-F11C-4DAA-93EB-CEBD94FF81A9}" name="locationLatitude" dataDxfId="103"/>
+    <tableColumn id="10" xr3:uid="{6A14EB46-0BF4-45C6-9048-E1B7D13E633A}" name="locationLongitude" dataDxfId="102"/>
+    <tableColumn id="11" xr3:uid="{9954429A-AA41-408C-BB04-D73EDB89D73F}" name="locationAltitude" dataDxfId="101"/>
+    <tableColumn id="12" xr3:uid="{39FEDA43-D994-4742-B319-3DFED43EF79B}" name="expeDesignDesc" dataDxfId="100"/>
+    <tableColumn id="13" xr3:uid="{C9F6A881-1CF1-4AD9-8305-B7E26FD78E3B}" name="expeDesignType" dataDxfId="99"/>
+    <tableColumn id="14" xr3:uid="{253A58C7-1A2A-4D25-9622-3AE33F89A685}" name="obsUnitLevelHierarchy" dataDxfId="98"/>
+    <tableColumn id="15" xr3:uid="{10DCEB5F-0BF5-4476-83E5-B973A516A8CD}" name="obsUnitDesc" dataDxfId="97"/>
+    <tableColumn id="16" xr3:uid="{0D36E7FE-2245-4B79-9A59-4C64590731A5}" name="growthFacilityDesc" dataDxfId="96"/>
+    <tableColumn id="17" xr3:uid="{599307E8-6E88-4D3F-BF48-ADF70D109D18}" name="growthFacilityType" dataDxfId="95"/>
+    <tableColumn id="18" xr3:uid="{63403E81-283C-4E2E-984D-9EFC0886E90C}" name="culturalPractice" dataDxfId="94"/>
+    <tableColumn id="19" xr3:uid="{E74D4B3A-67BC-482F-8485-FC7D9088A8B6}" name="expeDesignMap" dataDxfId="93"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}" name="person" displayName="person" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="83" dataDxfId="84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}" name="person" displayName="person" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="84" dataDxfId="85">
   <autoFilter ref="A1:F2" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{49A703DB-336A-4F60-9DA6-8249763A2765}" name="studyId" dataDxfId="90"/>
-    <tableColumn id="2" xr3:uid="{65039BF4-A122-4B88-8EB2-FD3ED61B8912}" name="personName" dataDxfId="89"/>
-    <tableColumn id="3" xr3:uid="{4B7588A4-B756-4E28-B8A4-AFB8D62031B4}" name="personEmail" dataDxfId="88"/>
-    <tableColumn id="4" xr3:uid="{639FC837-B543-4A62-B2C2-3EE761EF5EF7}" name="personId" dataDxfId="87"/>
-    <tableColumn id="5" xr3:uid="{593F31A8-CDAA-47CF-89F3-2902C6B8D3C8}" name="personRole" dataDxfId="86"/>
-    <tableColumn id="6" xr3:uid="{5FCF059F-31D5-4218-8D81-DC379C42EAF4}" name="personAffiliation" dataDxfId="85"/>
+    <tableColumn id="1" xr3:uid="{49A703DB-336A-4F60-9DA6-8249763A2765}" name="studyId" dataDxfId="91"/>
+    <tableColumn id="2" xr3:uid="{65039BF4-A122-4B88-8EB2-FD3ED61B8912}" name="personName" dataDxfId="90"/>
+    <tableColumn id="3" xr3:uid="{4B7588A4-B756-4E28-B8A4-AFB8D62031B4}" name="personEmail" dataDxfId="89"/>
+    <tableColumn id="4" xr3:uid="{639FC837-B543-4A62-B2C2-3EE761EF5EF7}" name="personId" dataDxfId="88"/>
+    <tableColumn id="5" xr3:uid="{593F31A8-CDAA-47CF-89F3-2902C6B8D3C8}" name="personRole" dataDxfId="87"/>
+    <tableColumn id="6" xr3:uid="{5FCF059F-31D5-4218-8D81-DC379C42EAF4}" name="personAffiliation" dataDxfId="86"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}" name="dataFile" displayName="dataFile" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="77" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}" name="dataFile" displayName="dataFile" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="78" dataDxfId="79">
   <autoFilter ref="A1:D2" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AD6A7B95-2E4C-4264-86B4-35031C8932E3}" name="studyId" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{A5C92CF7-B78F-4910-A250-8A16D6E7889C}" name="dataFileLink" dataDxfId="81"/>
-    <tableColumn id="3" xr3:uid="{620AC217-74DA-496A-9696-16EF7D98E86C}" name="dataFileDesc" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{79F128D7-FDA0-4F62-B04B-DAEE7E495850}" name="dataFileVersion" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{AD6A7B95-2E4C-4264-86B4-35031C8932E3}" name="studyId" dataDxfId="83"/>
+    <tableColumn id="2" xr3:uid="{A5C92CF7-B78F-4910-A250-8A16D6E7889C}" name="dataFileLink" dataDxfId="82"/>
+    <tableColumn id="3" xr3:uid="{620AC217-74DA-496A-9696-16EF7D98E86C}" name="dataFileDesc" dataDxfId="81"/>
+    <tableColumn id="4" xr3:uid="{79F128D7-FDA0-4F62-B04B-DAEE7E495850}" name="dataFileVersion" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}" name="biologicalMaterial" displayName="biologicalMaterial" ref="A1:X2" insertRow="1" totalsRowShown="0" headerRowDxfId="51" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}" name="biologicalMaterial" displayName="biologicalMaterial" ref="A1:X2" insertRow="1" totalsRowShown="0" headerRowDxfId="52" dataDxfId="53">
   <autoFilter ref="A1:X2" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}"/>
   <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{71E6992E-3AF7-4C8A-9C1E-930C105005E2}" name="studyId" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{BA8B45A2-9F79-4EE6-A38F-EF56D5CE4A1A}" name="biologicalMaterialId" dataDxfId="75"/>
-    <tableColumn id="3" xr3:uid="{546FEA19-FA9D-47D3-BF6E-57CDA029B0A3}" name="biologicalMaterialExtId" dataDxfId="74"/>
-    <tableColumn id="4" xr3:uid="{0DD21880-A5E2-4076-AA9F-554DE7C7E0D1}" name="organism" dataDxfId="73"/>
-    <tableColumn id="5" xr3:uid="{9760C8F1-7162-4A84-80C2-FBEC779AFAD0}" name="genus" dataDxfId="72"/>
-    <tableColumn id="6" xr3:uid="{D7026284-DE40-4B04-A583-983A0B5FB5BB}" name="species" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{22046373-BBD5-4919-AC4C-AA8E91D97026}" name="infraspecificName" dataDxfId="70"/>
-    <tableColumn id="8" xr3:uid="{579B0DCA-BD9C-4E7B-BB3B-3FB19A4CBCA3}" name="biologicalMaterialLatitude" dataDxfId="69"/>
-    <tableColumn id="9" xr3:uid="{A7E064AC-CDCF-4898-BEF3-07CF88887A4E}" name="biologicalMaterialLongitude" dataDxfId="68"/>
-    <tableColumn id="10" xr3:uid="{D55DD07C-0BE6-4D7D-80E1-B7195245711A}" name="biologicalMaterialAltitude" dataDxfId="67"/>
-    <tableColumn id="11" xr3:uid="{CA82A017-8E46-417C-9A1F-D7010C7B489F}" name="biologicalMaterialCoordUncertainty" dataDxfId="66"/>
-    <tableColumn id="12" xr3:uid="{16F6B082-1241-4094-AFDC-6E6F5B63F502}" name="biologicalMaterialPreprocessing" dataDxfId="65"/>
-    <tableColumn id="13" xr3:uid="{16F5564F-9F1B-4CEB-8DEC-4F46E89C2EB5}" name="materialSourceId" dataDxfId="64"/>
-    <tableColumn id="14" xr3:uid="{0AB5DA63-1709-41B8-9FAD-5B1A8A45E649}" name="materialSourceDoi" dataDxfId="63"/>
-    <tableColumn id="15" xr3:uid="{26116E4A-CA0A-4D6C-A863-AEA24B0E0C24}" name="materialSourceAccNumber" dataDxfId="62"/>
-    <tableColumn id="16" xr3:uid="{0C2E647E-5127-470F-859E-ED727EEFA3B9}" name="materialSourceAccName" dataDxfId="61"/>
-    <tableColumn id="17" xr3:uid="{B6097563-29EF-4C10-9096-04A2C164B15A}" name="materialSourceInstCode" dataDxfId="60"/>
-    <tableColumn id="18" xr3:uid="{BEA38246-EAA3-4450-B29F-D608607C2513}" name="materialSourceInstName" dataDxfId="59"/>
-    <tableColumn id="19" xr3:uid="{E8257013-CD5D-4534-9CD0-08D9EBBE7EF0}" name="materialSourceOtherIds" dataDxfId="58"/>
-    <tableColumn id="20" xr3:uid="{BE0E6D94-2ED0-4863-9DE5-9AA6BD4643D6}" name="materialSourceLatitude" dataDxfId="57"/>
-    <tableColumn id="21" xr3:uid="{BD849876-C99C-4475-87D4-DEECBE575F67}" name="materialSourceLongitude" dataDxfId="56"/>
-    <tableColumn id="22" xr3:uid="{0C871681-B897-43DD-A6BE-F03CAA6574F6}" name="materialSourceAltitude" dataDxfId="55"/>
-    <tableColumn id="23" xr3:uid="{ECC67BD8-3E1F-4A97-95B0-A9CCE07839CA}" name="materialSourceCoordUncertainty" dataDxfId="54"/>
-    <tableColumn id="24" xr3:uid="{C66E78D2-DB97-4D59-8D52-ECE79ED6BB86}" name="materialSourceDesc" dataDxfId="53"/>
+    <tableColumn id="1" xr3:uid="{71E6992E-3AF7-4C8A-9C1E-930C105005E2}" name="studyId" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{BA8B45A2-9F79-4EE6-A38F-EF56D5CE4A1A}" name="biologicalMaterialId" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{546FEA19-FA9D-47D3-BF6E-57CDA029B0A3}" name="biologicalMaterialExtId" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{0DD21880-A5E2-4076-AA9F-554DE7C7E0D1}" name="organism" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{9760C8F1-7162-4A84-80C2-FBEC779AFAD0}" name="genus" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{D7026284-DE40-4B04-A583-983A0B5FB5BB}" name="species" dataDxfId="72"/>
+    <tableColumn id="7" xr3:uid="{22046373-BBD5-4919-AC4C-AA8E91D97026}" name="infraspecificName" dataDxfId="71"/>
+    <tableColumn id="8" xr3:uid="{579B0DCA-BD9C-4E7B-BB3B-3FB19A4CBCA3}" name="biologicalMaterialLatitude" dataDxfId="70"/>
+    <tableColumn id="9" xr3:uid="{A7E064AC-CDCF-4898-BEF3-07CF88887A4E}" name="biologicalMaterialLongitude" dataDxfId="69"/>
+    <tableColumn id="10" xr3:uid="{D55DD07C-0BE6-4D7D-80E1-B7195245711A}" name="biologicalMaterialAltitude" dataDxfId="68"/>
+    <tableColumn id="11" xr3:uid="{CA82A017-8E46-417C-9A1F-D7010C7B489F}" name="biologicalMaterialCoordUncertainty" dataDxfId="67"/>
+    <tableColumn id="12" xr3:uid="{16F6B082-1241-4094-AFDC-6E6F5B63F502}" name="biologicalMaterialPreprocessing" dataDxfId="66"/>
+    <tableColumn id="13" xr3:uid="{16F5564F-9F1B-4CEB-8DEC-4F46E89C2EB5}" name="materialSourceId" dataDxfId="65"/>
+    <tableColumn id="14" xr3:uid="{0AB5DA63-1709-41B8-9FAD-5B1A8A45E649}" name="materialSourceDoi" dataDxfId="64"/>
+    <tableColumn id="15" xr3:uid="{26116E4A-CA0A-4D6C-A863-AEA24B0E0C24}" name="materialSourceAccNumber" dataDxfId="63"/>
+    <tableColumn id="16" xr3:uid="{0C2E647E-5127-470F-859E-ED727EEFA3B9}" name="materialSourceAccName" dataDxfId="62"/>
+    <tableColumn id="17" xr3:uid="{B6097563-29EF-4C10-9096-04A2C164B15A}" name="materialSourceInstCode" dataDxfId="61"/>
+    <tableColumn id="18" xr3:uid="{BEA38246-EAA3-4450-B29F-D608607C2513}" name="materialSourceInstName" dataDxfId="60"/>
+    <tableColumn id="19" xr3:uid="{E8257013-CD5D-4534-9CD0-08D9EBBE7EF0}" name="materialSourceOtherIds" dataDxfId="59"/>
+    <tableColumn id="20" xr3:uid="{BE0E6D94-2ED0-4863-9DE5-9AA6BD4643D6}" name="materialSourceLatitude" dataDxfId="58"/>
+    <tableColumn id="21" xr3:uid="{BD849876-C99C-4475-87D4-DEECBE575F67}" name="materialSourceLongitude" dataDxfId="57"/>
+    <tableColumn id="22" xr3:uid="{0C871681-B897-43DD-A6BE-F03CAA6574F6}" name="materialSourceAltitude" dataDxfId="56"/>
+    <tableColumn id="23" xr3:uid="{ECC67BD8-3E1F-4A97-95B0-A9CCE07839CA}" name="materialSourceCoordUncertainty" dataDxfId="55"/>
+    <tableColumn id="24" xr3:uid="{C66E78D2-DB97-4D59-8D52-ECE79ED6BB86}" name="materialSourceDesc" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}" name="environment" displayName="environment" ref="A1:C2" insertRow="1" totalsRowShown="0" headerRowDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}" name="environment" displayName="environment" ref="A1:C2" insertRow="1" totalsRowShown="0" headerRowDxfId="48">
   <autoFilter ref="A1:C2" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{08C0BD82-D970-44E6-99E3-B4872FECEFE5}" name="studyId" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{F9DC7CC5-88B3-4A9A-B462-9FB971836B81}" name="envParam" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{65E72A00-3C03-4A17-922C-EE6A4A3D8D80}" name="envParamValue" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{08C0BD82-D970-44E6-99E3-B4872FECEFE5}" name="studyId" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{F9DC7CC5-88B3-4A9A-B462-9FB971836B81}" name="envParam" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{65E72A00-3C03-4A17-922C-EE6A4A3D8D80}" name="envParamValue" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}" name="experimentalFactor" displayName="experimentalFactor" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}" name="experimentalFactor" displayName="experimentalFactor" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="43">
   <autoFilter ref="A1:D2" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:F2" insertRow="1" totalsRowShown="0" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:F2" insertRow="1" totalsRowShown="0" dataDxfId="36">
   <autoFilter ref="A1:F2" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{DB25986C-BD6F-40F9-A226-C9A11BBDF460}" name="studyId" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{6EE72788-DEAD-4FC0-9383-C6415EC5E8A5}" name="obsUnitId" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{0DDCD5FF-AC45-4794-9B28-BBD982C1FB84}" name="eventType" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{DB25986C-BD6F-40F9-A226-C9A11BBDF460}" name="studyId" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{6EE72788-DEAD-4FC0-9383-C6415EC5E8A5}" name="obsUnitId" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{0DDCD5FF-AC45-4794-9B28-BBD982C1FB84}" name="eventType" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:G2" insertRow="1" totalsRowShown="0" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:G2" insertRow="1" totalsRowShown="0" dataDxfId="28">
   <autoFilter ref="A1:G2" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17939,7 +17963,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:S977"/>
+  <dimension ref="A1:T977"/>
   <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="13" width="20.4609375" customWidth="1"/>
@@ -17948,112 +17972,117 @@
     <col min="16315" max="16384" width="11.4609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="52" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="52" t="s">
+        <v>674</v>
+      </c>
+      <c r="C1" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="D1" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="E1" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="F1" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="G1" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="H1" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="52" t="s">
+      <c r="I1" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="J1" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="K1" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="L1" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="52" t="s">
+      <c r="M1" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="M1" s="53" t="s">
+      <c r="N1" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="N1" s="53" t="s">
+      <c r="O1" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="O1" s="52" t="s">
+      <c r="P1" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="P1" s="52" t="s">
+      <c r="Q1" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="R1" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="R1" s="53" t="s">
+      <c r="S1" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="S1" s="53" t="s">
+      <c r="T1" s="53" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="54" t="s">
         <v>672</v>
       </c>
-      <c r="B2" s="55"/>
+      <c r="B2" s="54"/>
       <c r="C2" s="55"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="54"/>
       <c r="F2" s="55"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="54"/>
       <c r="I2" s="55"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="54"/>
       <c r="L2" s="55"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="54"/>
       <c r="O2" s="55"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="54"/>
       <c r="R2" s="55"/>
-      <c r="S2" s="54"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="54"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="54" t="s">
         <v>673</v>
       </c>
-      <c r="B3" s="55"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="55"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="54"/>
       <c r="F3" s="55"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="54"/>
       <c r="I3" s="55"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="54"/>
       <c r="L3" s="55"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="54"/>
       <c r="O3" s="55"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="55"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="54"/>
       <c r="R3" s="55"/>
-      <c r="S3" s="54"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="54"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56"/>
       <c r="B4" s="56"/>
       <c r="C4" s="56"/>
@@ -18074,7 +18103,7 @@
       <c r="R4" s="56"/>
       <c r="S4" s="56"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56"/>
       <c r="B5" s="56"/>
       <c r="C5" s="56"/>
@@ -18095,7 +18124,7 @@
       <c r="R5" s="56"/>
       <c r="S5" s="56"/>
     </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56"/>
       <c r="B6" s="56"/>
       <c r="C6" s="56"/>
@@ -18116,7 +18145,7 @@
       <c r="R6" s="56"/>
       <c r="S6" s="56"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56"/>
       <c r="B7" s="56"/>
       <c r="C7" s="56"/>
@@ -18137,7 +18166,7 @@
       <c r="R7" s="56"/>
       <c r="S7" s="56"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56"/>
       <c r="B8" s="56"/>
       <c r="C8" s="56"/>
@@ -18158,14 +18187,14 @@
       <c r="R8" s="56"/>
       <c r="S8" s="56"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -19128,6 +19157,11 @@
     <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B3" xr:uid="{8325CA2E-9AEF-4B88-A4C2-C6DFDAD87C22}">
+      <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">

--- a/Templates/MIAPPE_Spreadsheet_Template.xlsx
+++ b/Templates/MIAPPE_Spreadsheet_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\MIAPPE\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A410AC2B-76C3-49BA-BF00-555A165A057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD08D038-182B-4D7F-9759-41F842E223CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="891" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,14 @@
     <sheet name="Data file" sheetId="5" r:id="rId5"/>
     <sheet name="Biological Material" sheetId="6" r:id="rId6"/>
     <sheet name="Environment" sheetId="7" r:id="rId7"/>
-    <sheet name="Experimental Factor" sheetId="8" r:id="rId8"/>
-    <sheet name="Event" sheetId="9" r:id="rId9"/>
-    <sheet name="Observation Unit" sheetId="10" r:id="rId10"/>
-    <sheet name="Sample" sheetId="11" r:id="rId11"/>
-    <sheet name="Observed Variable" sheetId="12" r:id="rId12"/>
-    <sheet name="Appendix1 Environment" sheetId="13" r:id="rId13"/>
-    <sheet name="Appendix2 Experimental Factor" sheetId="14" r:id="rId14"/>
+    <sheet name="Environment Parameters" sheetId="15" r:id="rId8"/>
+    <sheet name="Experimental Factor" sheetId="8" r:id="rId9"/>
+    <sheet name="Event" sheetId="9" r:id="rId10"/>
+    <sheet name="Observation Unit" sheetId="10" r:id="rId11"/>
+    <sheet name="Sample" sheetId="11" r:id="rId12"/>
+    <sheet name="Observed Variable" sheetId="12" r:id="rId13"/>
+    <sheet name="Appendix1 Environment" sheetId="13" r:id="rId14"/>
+    <sheet name="Appendix2 Experimental Factor" sheetId="14" r:id="rId15"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="682">
   <si>
     <t>README</t>
   </si>
@@ -2256,6 +2257,27 @@
   <si>
     <t>parentStudyId</t>
   </si>
+  <si>
+    <t>envParamAccession</t>
+  </si>
+  <si>
+    <t>envParamDesc</t>
+  </si>
+  <si>
+    <t>seed rate</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/AGRO_00000202</t>
+  </si>
+  <si>
+    <t>Mass of the seeds sown on a given surface area.</t>
+  </si>
+  <si>
+    <t>humidity regimen</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/EO_0007197</t>
+  </si>
 </sst>
 </file>
 
@@ -2264,7 +2286,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2414,6 +2436,26 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2469,10 +2511,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2632,11 +2675,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="131">
+  <dxfs count="132">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -5157,15 +5222,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="MiappeStyle" pivot="0" count="9" xr9:uid="{59C54380-D204-4007-9CC6-0890CCDEE3C9}">
-      <tableStyleElement type="wholeTable" dxfId="130"/>
-      <tableStyleElement type="headerRow" dxfId="129"/>
-      <tableStyleElement type="totalRow" dxfId="128"/>
-      <tableStyleElement type="firstColumn" dxfId="127"/>
-      <tableStyleElement type="lastColumn" dxfId="126"/>
-      <tableStyleElement type="firstRowStripe" dxfId="125"/>
-      <tableStyleElement type="secondRowStripe" dxfId="124"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="123"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="122"/>
+      <tableStyleElement type="wholeTable" dxfId="131"/>
+      <tableStyleElement type="headerRow" dxfId="130"/>
+      <tableStyleElement type="totalRow" dxfId="129"/>
+      <tableStyleElement type="firstColumn" dxfId="128"/>
+      <tableStyleElement type="lastColumn" dxfId="127"/>
+      <tableStyleElement type="firstRowStripe" dxfId="126"/>
+      <tableStyleElement type="secondRowStripe" dxfId="125"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="124"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="123"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5180,205 +5245,217 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}" name="investigation" displayName="investigation" ref="A1:H2" totalsRowShown="0" headerRowDxfId="112" dataDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}" name="investigation" displayName="investigation" ref="A1:H2" totalsRowShown="0" headerRowDxfId="113" dataDxfId="114">
   <autoFilter ref="A1:H2" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{25F01F79-3E24-44AF-B5E3-4EB20FD9A360}" name="investigationId" dataDxfId="121"/>
-    <tableColumn id="2" xr3:uid="{16E59F0F-AC6D-4504-A428-E7D7AC601401}" name="investigationTitle" dataDxfId="120"/>
-    <tableColumn id="3" xr3:uid="{4668A34F-CEFF-43A7-84AA-B014E3A90F47}" name="investigationDescription" dataDxfId="119"/>
-    <tableColumn id="4" xr3:uid="{403353FA-EBA5-418F-8273-81472CDF29D4}" name="submissionDate" dataDxfId="118"/>
-    <tableColumn id="5" xr3:uid="{18E43DB3-511F-4E0E-B357-B4A6E40F0660}" name="publicReleaseDate" dataDxfId="117"/>
-    <tableColumn id="6" xr3:uid="{91C01C8C-69AF-4B74-BA16-1C962EDAF32D}" name="license" dataDxfId="116"/>
-    <tableColumn id="7" xr3:uid="{E94BB99A-781A-4442-AD9C-7E4D99028DC9}" name="miappeVersion" dataDxfId="115"/>
-    <tableColumn id="8" xr3:uid="{91B9E445-65BD-412A-95C1-EA371F946FCA}" name="associatedPublication" dataDxfId="114"/>
+    <tableColumn id="1" xr3:uid="{25F01F79-3E24-44AF-B5E3-4EB20FD9A360}" name="investigationId" dataDxfId="122"/>
+    <tableColumn id="2" xr3:uid="{16E59F0F-AC6D-4504-A428-E7D7AC601401}" name="investigationTitle" dataDxfId="121"/>
+    <tableColumn id="3" xr3:uid="{4668A34F-CEFF-43A7-84AA-B014E3A90F47}" name="investigationDescription" dataDxfId="120"/>
+    <tableColumn id="4" xr3:uid="{403353FA-EBA5-418F-8273-81472CDF29D4}" name="submissionDate" dataDxfId="119"/>
+    <tableColumn id="5" xr3:uid="{18E43DB3-511F-4E0E-B357-B4A6E40F0660}" name="publicReleaseDate" dataDxfId="118"/>
+    <tableColumn id="6" xr3:uid="{91C01C8C-69AF-4B74-BA16-1C962EDAF32D}" name="license" dataDxfId="117"/>
+    <tableColumn id="7" xr3:uid="{E94BB99A-781A-4442-AD9C-7E4D99028DC9}" name="miappeVersion" dataDxfId="116"/>
+    <tableColumn id="8" xr3:uid="{91B9E445-65BD-412A-95C1-EA371F946FCA}" name="associatedPublication" dataDxfId="115"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="19" dataDxfId="20">
-  <autoFilter ref="A1:G2" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:G2" insertRow="1" totalsRowShown="0" dataDxfId="29">
+  <autoFilter ref="A1:G2" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{92A1E618-2F85-46E4-B7EF-76ED045C215B}" name="obsUnitId" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{A0DFEC37-340B-4DF8-907B-A9769602FD28}" name="sampleId" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{D455AF29-BE41-4DDA-A9B2-A46F4EEA6767}" name="developmentStage" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{C24109D3-E8A6-4810-A0A6-ACD6730F0D08}" name="anatomicalEntity" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{5C630D57-B424-4325-BC0C-BEEBEDC89DBB}" name="sampleDesc" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{CDEC6C64-2387-4FCF-9A2C-63F54020D0A0}" name="collectionDate" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{FFB2A4F7-3C7D-4BC5-AD9E-C14C20349305}" name="externalId" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:Q2" insertRow="1" totalsRowShown="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="20" dataDxfId="21">
+  <autoFilter ref="A1:G2" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{92A1E618-2F85-46E4-B7EF-76ED045C215B}" name="obsUnitId" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{A0DFEC37-340B-4DF8-907B-A9769602FD28}" name="sampleId" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{D455AF29-BE41-4DDA-A9B2-A46F4EEA6767}" name="developmentStage" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{C24109D3-E8A6-4810-A0A6-ACD6730F0D08}" name="anatomicalEntity" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{5C630D57-B424-4325-BC0C-BEEBEDC89DBB}" name="sampleDesc" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{CDEC6C64-2387-4FCF-9A2C-63F54020D0A0}" name="collectionDate" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{FFB2A4F7-3C7D-4BC5-AD9E-C14C20349305}" name="externalId" dataDxfId="22"/>
+  </tableColumns>
+  <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:Q2" insertRow="1" totalsRowShown="0" dataDxfId="2">
   <autoFilter ref="A1:Q2" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccNumber" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccessionNumber" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccessionNumber" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccNumber" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccNumber" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccNumber" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="timeScale" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccNumber" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccessionNumber" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccessionNumber" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccNumber" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccNumber" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccNumber" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="timeScale" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:T3" totalsRowShown="0" dataDxfId="92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:T3" totalsRowShown="0" dataDxfId="93">
   <autoFilter ref="A1:T3" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="111"/>
-    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="parentStudyId" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="110"/>
-    <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="109"/>
-    <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="108"/>
-    <tableColumn id="5" xr3:uid="{E557DB42-3379-4598-AAF9-21798BC64DAB}" name="studyEndDate" dataDxfId="107"/>
-    <tableColumn id="6" xr3:uid="{1EEA2EC5-CA19-40B4-9DFB-2DE9A9E916EA}" name="contactInst" dataDxfId="106"/>
-    <tableColumn id="7" xr3:uid="{E0A5C222-CFE5-4E9C-8E84-0892043DBD21}" name="locationCountry" dataDxfId="105"/>
-    <tableColumn id="8" xr3:uid="{7B635D2A-56C5-48B0-A880-E33ADE030AB1}" name="siteName" dataDxfId="104"/>
-    <tableColumn id="9" xr3:uid="{2F8227C3-F11C-4DAA-93EB-CEBD94FF81A9}" name="locationLatitude" dataDxfId="103"/>
-    <tableColumn id="10" xr3:uid="{6A14EB46-0BF4-45C6-9048-E1B7D13E633A}" name="locationLongitude" dataDxfId="102"/>
-    <tableColumn id="11" xr3:uid="{9954429A-AA41-408C-BB04-D73EDB89D73F}" name="locationAltitude" dataDxfId="101"/>
-    <tableColumn id="12" xr3:uid="{39FEDA43-D994-4742-B319-3DFED43EF79B}" name="expeDesignDesc" dataDxfId="100"/>
-    <tableColumn id="13" xr3:uid="{C9F6A881-1CF1-4AD9-8305-B7E26FD78E3B}" name="expeDesignType" dataDxfId="99"/>
-    <tableColumn id="14" xr3:uid="{253A58C7-1A2A-4D25-9622-3AE33F89A685}" name="obsUnitLevelHierarchy" dataDxfId="98"/>
-    <tableColumn id="15" xr3:uid="{10DCEB5F-0BF5-4476-83E5-B973A516A8CD}" name="obsUnitDesc" dataDxfId="97"/>
-    <tableColumn id="16" xr3:uid="{0D36E7FE-2245-4B79-9A59-4C64590731A5}" name="growthFacilityDesc" dataDxfId="96"/>
-    <tableColumn id="17" xr3:uid="{599307E8-6E88-4D3F-BF48-ADF70D109D18}" name="growthFacilityType" dataDxfId="95"/>
-    <tableColumn id="18" xr3:uid="{63403E81-283C-4E2E-984D-9EFC0886E90C}" name="culturalPractice" dataDxfId="94"/>
-    <tableColumn id="19" xr3:uid="{E74D4B3A-67BC-482F-8485-FC7D9088A8B6}" name="expeDesignMap" dataDxfId="93"/>
+    <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="112"/>
+    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="parentStudyId" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="111"/>
+    <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="110"/>
+    <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="109"/>
+    <tableColumn id="5" xr3:uid="{E557DB42-3379-4598-AAF9-21798BC64DAB}" name="studyEndDate" dataDxfId="108"/>
+    <tableColumn id="6" xr3:uid="{1EEA2EC5-CA19-40B4-9DFB-2DE9A9E916EA}" name="contactInst" dataDxfId="107"/>
+    <tableColumn id="7" xr3:uid="{E0A5C222-CFE5-4E9C-8E84-0892043DBD21}" name="locationCountry" dataDxfId="106"/>
+    <tableColumn id="8" xr3:uid="{7B635D2A-56C5-48B0-A880-E33ADE030AB1}" name="siteName" dataDxfId="105"/>
+    <tableColumn id="9" xr3:uid="{2F8227C3-F11C-4DAA-93EB-CEBD94FF81A9}" name="locationLatitude" dataDxfId="104"/>
+    <tableColumn id="10" xr3:uid="{6A14EB46-0BF4-45C6-9048-E1B7D13E633A}" name="locationLongitude" dataDxfId="103"/>
+    <tableColumn id="11" xr3:uid="{9954429A-AA41-408C-BB04-D73EDB89D73F}" name="locationAltitude" dataDxfId="102"/>
+    <tableColumn id="12" xr3:uid="{39FEDA43-D994-4742-B319-3DFED43EF79B}" name="expeDesignDesc" dataDxfId="101"/>
+    <tableColumn id="13" xr3:uid="{C9F6A881-1CF1-4AD9-8305-B7E26FD78E3B}" name="expeDesignType" dataDxfId="100"/>
+    <tableColumn id="14" xr3:uid="{253A58C7-1A2A-4D25-9622-3AE33F89A685}" name="obsUnitLevelHierarchy" dataDxfId="99"/>
+    <tableColumn id="15" xr3:uid="{10DCEB5F-0BF5-4476-83E5-B973A516A8CD}" name="obsUnitDesc" dataDxfId="98"/>
+    <tableColumn id="16" xr3:uid="{0D36E7FE-2245-4B79-9A59-4C64590731A5}" name="growthFacilityDesc" dataDxfId="97"/>
+    <tableColumn id="17" xr3:uid="{599307E8-6E88-4D3F-BF48-ADF70D109D18}" name="growthFacilityType" dataDxfId="96"/>
+    <tableColumn id="18" xr3:uid="{63403E81-283C-4E2E-984D-9EFC0886E90C}" name="culturalPractice" dataDxfId="95"/>
+    <tableColumn id="19" xr3:uid="{E74D4B3A-67BC-482F-8485-FC7D9088A8B6}" name="expeDesignMap" dataDxfId="94"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}" name="person" displayName="person" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="84" dataDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}" name="person" displayName="person" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="85" dataDxfId="86">
   <autoFilter ref="A1:F2" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{49A703DB-336A-4F60-9DA6-8249763A2765}" name="studyId" dataDxfId="91"/>
-    <tableColumn id="2" xr3:uid="{65039BF4-A122-4B88-8EB2-FD3ED61B8912}" name="personName" dataDxfId="90"/>
-    <tableColumn id="3" xr3:uid="{4B7588A4-B756-4E28-B8A4-AFB8D62031B4}" name="personEmail" dataDxfId="89"/>
-    <tableColumn id="4" xr3:uid="{639FC837-B543-4A62-B2C2-3EE761EF5EF7}" name="personId" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{593F31A8-CDAA-47CF-89F3-2902C6B8D3C8}" name="personRole" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{5FCF059F-31D5-4218-8D81-DC379C42EAF4}" name="personAffiliation" dataDxfId="86"/>
+    <tableColumn id="1" xr3:uid="{49A703DB-336A-4F60-9DA6-8249763A2765}" name="studyId" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{65039BF4-A122-4B88-8EB2-FD3ED61B8912}" name="personName" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{4B7588A4-B756-4E28-B8A4-AFB8D62031B4}" name="personEmail" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{639FC837-B543-4A62-B2C2-3EE761EF5EF7}" name="personId" dataDxfId="89"/>
+    <tableColumn id="5" xr3:uid="{593F31A8-CDAA-47CF-89F3-2902C6B8D3C8}" name="personRole" dataDxfId="88"/>
+    <tableColumn id="6" xr3:uid="{5FCF059F-31D5-4218-8D81-DC379C42EAF4}" name="personAffiliation" dataDxfId="87"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}" name="dataFile" displayName="dataFile" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="78" dataDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}" name="dataFile" displayName="dataFile" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="79" dataDxfId="80">
   <autoFilter ref="A1:D2" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AD6A7B95-2E4C-4264-86B4-35031C8932E3}" name="studyId" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{A5C92CF7-B78F-4910-A250-8A16D6E7889C}" name="dataFileLink" dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{620AC217-74DA-496A-9696-16EF7D98E86C}" name="dataFileDesc" dataDxfId="81"/>
-    <tableColumn id="4" xr3:uid="{79F128D7-FDA0-4F62-B04B-DAEE7E495850}" name="dataFileVersion" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{AD6A7B95-2E4C-4264-86B4-35031C8932E3}" name="studyId" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{A5C92CF7-B78F-4910-A250-8A16D6E7889C}" name="dataFileLink" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{620AC217-74DA-496A-9696-16EF7D98E86C}" name="dataFileDesc" dataDxfId="82"/>
+    <tableColumn id="4" xr3:uid="{79F128D7-FDA0-4F62-B04B-DAEE7E495850}" name="dataFileVersion" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}" name="biologicalMaterial" displayName="biologicalMaterial" ref="A1:X2" insertRow="1" totalsRowShown="0" headerRowDxfId="52" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}" name="biologicalMaterial" displayName="biologicalMaterial" ref="A1:X2" insertRow="1" totalsRowShown="0" headerRowDxfId="53" dataDxfId="54">
   <autoFilter ref="A1:X2" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}"/>
   <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{71E6992E-3AF7-4C8A-9C1E-930C105005E2}" name="studyId" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{BA8B45A2-9F79-4EE6-A38F-EF56D5CE4A1A}" name="biologicalMaterialId" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{546FEA19-FA9D-47D3-BF6E-57CDA029B0A3}" name="biologicalMaterialExtId" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{0DD21880-A5E2-4076-AA9F-554DE7C7E0D1}" name="organism" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{9760C8F1-7162-4A84-80C2-FBEC779AFAD0}" name="genus" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{D7026284-DE40-4B04-A583-983A0B5FB5BB}" name="species" dataDxfId="72"/>
-    <tableColumn id="7" xr3:uid="{22046373-BBD5-4919-AC4C-AA8E91D97026}" name="infraspecificName" dataDxfId="71"/>
-    <tableColumn id="8" xr3:uid="{579B0DCA-BD9C-4E7B-BB3B-3FB19A4CBCA3}" name="biologicalMaterialLatitude" dataDxfId="70"/>
-    <tableColumn id="9" xr3:uid="{A7E064AC-CDCF-4898-BEF3-07CF88887A4E}" name="biologicalMaterialLongitude" dataDxfId="69"/>
-    <tableColumn id="10" xr3:uid="{D55DD07C-0BE6-4D7D-80E1-B7195245711A}" name="biologicalMaterialAltitude" dataDxfId="68"/>
-    <tableColumn id="11" xr3:uid="{CA82A017-8E46-417C-9A1F-D7010C7B489F}" name="biologicalMaterialCoordUncertainty" dataDxfId="67"/>
-    <tableColumn id="12" xr3:uid="{16F6B082-1241-4094-AFDC-6E6F5B63F502}" name="biologicalMaterialPreprocessing" dataDxfId="66"/>
-    <tableColumn id="13" xr3:uid="{16F5564F-9F1B-4CEB-8DEC-4F46E89C2EB5}" name="materialSourceId" dataDxfId="65"/>
-    <tableColumn id="14" xr3:uid="{0AB5DA63-1709-41B8-9FAD-5B1A8A45E649}" name="materialSourceDoi" dataDxfId="64"/>
-    <tableColumn id="15" xr3:uid="{26116E4A-CA0A-4D6C-A863-AEA24B0E0C24}" name="materialSourceAccNumber" dataDxfId="63"/>
-    <tableColumn id="16" xr3:uid="{0C2E647E-5127-470F-859E-ED727EEFA3B9}" name="materialSourceAccName" dataDxfId="62"/>
-    <tableColumn id="17" xr3:uid="{B6097563-29EF-4C10-9096-04A2C164B15A}" name="materialSourceInstCode" dataDxfId="61"/>
-    <tableColumn id="18" xr3:uid="{BEA38246-EAA3-4450-B29F-D608607C2513}" name="materialSourceInstName" dataDxfId="60"/>
-    <tableColumn id="19" xr3:uid="{E8257013-CD5D-4534-9CD0-08D9EBBE7EF0}" name="materialSourceOtherIds" dataDxfId="59"/>
-    <tableColumn id="20" xr3:uid="{BE0E6D94-2ED0-4863-9DE5-9AA6BD4643D6}" name="materialSourceLatitude" dataDxfId="58"/>
-    <tableColumn id="21" xr3:uid="{BD849876-C99C-4475-87D4-DEECBE575F67}" name="materialSourceLongitude" dataDxfId="57"/>
-    <tableColumn id="22" xr3:uid="{0C871681-B897-43DD-A6BE-F03CAA6574F6}" name="materialSourceAltitude" dataDxfId="56"/>
-    <tableColumn id="23" xr3:uid="{ECC67BD8-3E1F-4A97-95B0-A9CCE07839CA}" name="materialSourceCoordUncertainty" dataDxfId="55"/>
-    <tableColumn id="24" xr3:uid="{C66E78D2-DB97-4D59-8D52-ECE79ED6BB86}" name="materialSourceDesc" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{71E6992E-3AF7-4C8A-9C1E-930C105005E2}" name="studyId" dataDxfId="78"/>
+    <tableColumn id="2" xr3:uid="{BA8B45A2-9F79-4EE6-A38F-EF56D5CE4A1A}" name="biologicalMaterialId" dataDxfId="77"/>
+    <tableColumn id="3" xr3:uid="{546FEA19-FA9D-47D3-BF6E-57CDA029B0A3}" name="biologicalMaterialExtId" dataDxfId="76"/>
+    <tableColumn id="4" xr3:uid="{0DD21880-A5E2-4076-AA9F-554DE7C7E0D1}" name="organism" dataDxfId="75"/>
+    <tableColumn id="5" xr3:uid="{9760C8F1-7162-4A84-80C2-FBEC779AFAD0}" name="genus" dataDxfId="74"/>
+    <tableColumn id="6" xr3:uid="{D7026284-DE40-4B04-A583-983A0B5FB5BB}" name="species" dataDxfId="73"/>
+    <tableColumn id="7" xr3:uid="{22046373-BBD5-4919-AC4C-AA8E91D97026}" name="infraspecificName" dataDxfId="72"/>
+    <tableColumn id="8" xr3:uid="{579B0DCA-BD9C-4E7B-BB3B-3FB19A4CBCA3}" name="biologicalMaterialLatitude" dataDxfId="71"/>
+    <tableColumn id="9" xr3:uid="{A7E064AC-CDCF-4898-BEF3-07CF88887A4E}" name="biologicalMaterialLongitude" dataDxfId="70"/>
+    <tableColumn id="10" xr3:uid="{D55DD07C-0BE6-4D7D-80E1-B7195245711A}" name="biologicalMaterialAltitude" dataDxfId="69"/>
+    <tableColumn id="11" xr3:uid="{CA82A017-8E46-417C-9A1F-D7010C7B489F}" name="biologicalMaterialCoordUncertainty" dataDxfId="68"/>
+    <tableColumn id="12" xr3:uid="{16F6B082-1241-4094-AFDC-6E6F5B63F502}" name="biologicalMaterialPreprocessing" dataDxfId="67"/>
+    <tableColumn id="13" xr3:uid="{16F5564F-9F1B-4CEB-8DEC-4F46E89C2EB5}" name="materialSourceId" dataDxfId="66"/>
+    <tableColumn id="14" xr3:uid="{0AB5DA63-1709-41B8-9FAD-5B1A8A45E649}" name="materialSourceDoi" dataDxfId="65"/>
+    <tableColumn id="15" xr3:uid="{26116E4A-CA0A-4D6C-A863-AEA24B0E0C24}" name="materialSourceAccNumber" dataDxfId="64"/>
+    <tableColumn id="16" xr3:uid="{0C2E647E-5127-470F-859E-ED727EEFA3B9}" name="materialSourceAccName" dataDxfId="63"/>
+    <tableColumn id="17" xr3:uid="{B6097563-29EF-4C10-9096-04A2C164B15A}" name="materialSourceInstCode" dataDxfId="62"/>
+    <tableColumn id="18" xr3:uid="{BEA38246-EAA3-4450-B29F-D608607C2513}" name="materialSourceInstName" dataDxfId="61"/>
+    <tableColumn id="19" xr3:uid="{E8257013-CD5D-4534-9CD0-08D9EBBE7EF0}" name="materialSourceOtherIds" dataDxfId="60"/>
+    <tableColumn id="20" xr3:uid="{BE0E6D94-2ED0-4863-9DE5-9AA6BD4643D6}" name="materialSourceLatitude" dataDxfId="59"/>
+    <tableColumn id="21" xr3:uid="{BD849876-C99C-4475-87D4-DEECBE575F67}" name="materialSourceLongitude" dataDxfId="58"/>
+    <tableColumn id="22" xr3:uid="{0C871681-B897-43DD-A6BE-F03CAA6574F6}" name="materialSourceAltitude" dataDxfId="57"/>
+    <tableColumn id="23" xr3:uid="{ECC67BD8-3E1F-4A97-95B0-A9CCE07839CA}" name="materialSourceCoordUncertainty" dataDxfId="56"/>
+    <tableColumn id="24" xr3:uid="{C66E78D2-DB97-4D59-8D52-ECE79ED6BB86}" name="materialSourceDesc" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}" name="environment" displayName="environment" ref="A1:C2" insertRow="1" totalsRowShown="0" headerRowDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}" name="environment" displayName="environment" ref="A1:C2" insertRow="1" totalsRowShown="0" headerRowDxfId="49">
   <autoFilter ref="A1:C2" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{08C0BD82-D970-44E6-99E3-B4872FECEFE5}" name="studyId" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{F9DC7CC5-88B3-4A9A-B462-9FB971836B81}" name="envParam" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{65E72A00-3C03-4A17-922C-EE6A4A3D8D80}" name="envParamValue" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{08C0BD82-D970-44E6-99E3-B4872FECEFE5}" name="studyId" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{F9DC7CC5-88B3-4A9A-B462-9FB971836B81}" name="envParam" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{65E72A00-3C03-4A17-922C-EE6A4A3D8D80}" name="envParamValue" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}" name="experimentalFactor" displayName="experimentalFactor" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="43">
-  <autoFilter ref="A1:D2" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}" name="environmentParameters" displayName="environmentParameters" ref="A1:C3" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:C3" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{5E761B2A-3F92-4181-AF5D-F423F0564A09}" name="envParam"/>
+    <tableColumn id="2" xr3:uid="{859D023A-B6BE-4E62-A854-739263E5E0C9}" name="envParamAccession" dataCellStyle="Hyperlink"/>
+    <tableColumn id="3" xr3:uid="{86E20B70-FB31-402D-8CAA-272E40CA937F}" name="envParamDesc"/>
   </tableColumns>
-  <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:F2" insertRow="1" totalsRowShown="0" dataDxfId="36">
-  <autoFilter ref="A1:F2" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{DB25986C-BD6F-40F9-A226-C9A11BBDF460}" name="studyId" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{6EE72788-DEAD-4FC0-9383-C6415EC5E8A5}" name="obsUnitId" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{0DDCD5FF-AC45-4794-9B28-BBD982C1FB84}" name="eventType" dataDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}" name="experimentalFactor" displayName="experimentalFactor" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="44">
+  <autoFilter ref="A1:D2" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:G2" insertRow="1" totalsRowShown="0" dataDxfId="28">
-  <autoFilter ref="A1:G2" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:F2" insertRow="1" totalsRowShown="0" dataDxfId="37">
+  <autoFilter ref="A1:F2" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{DB25986C-BD6F-40F9-A226-C9A11BBDF460}" name="studyId" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{6EE72788-DEAD-4FC0-9383-C6415EC5E8A5}" name="obsUnitId" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{0DDCD5FF-AC45-4794-9B28-BBD982C1FB84}" name="eventType" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9897,6 +9974,1165 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:M997"/>
+  <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="6" width="20.4609375" customWidth="1"/>
+    <col min="7" max="13" width="43.3046875" customWidth="1"/>
+    <col min="16384" max="16384" width="11.4609375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="42" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" s="52" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>303</v>
+      </c>
+      <c r="F1" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+    </row>
+    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="54"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+    </row>
+    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+    </row>
+    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+    </row>
+    <row r="5" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+    </row>
+    <row r="6" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="56"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+    </row>
+    <row r="7" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+    </row>
+    <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="56"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+    </row>
+    <row r="9" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="40"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+    </row>
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{649E6E49-1C43-4DBC-A22C-62A99DEF1F6A}">
+      <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -11060,7 +12296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:M997"/>
   <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -12215,7 +13451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -13433,7 +14669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0000FF"/>
@@ -15494,7 +16730,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0000FF"/>
@@ -23690,9 +24926,12 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{F0012BD8-AD23-4059-8955-C8C950130C4D}">
       <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{D23A136B-F06D-463E-A5F3-58A48D58102D}">
+      <formula1>INDIRECT("environmentParameters[envParam]")</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -23704,6 +24943,59 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC78D81E-B798-4ACE-A55A-BBC317916E2E}">
+  <sheetPr>
+    <tabColor theme="1" tint="0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.53515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="63" t="s">
+        <v>271</v>
+      </c>
+      <c r="B1" s="63" t="s">
+        <v>675</v>
+      </c>
+      <c r="C1" s="63" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="64" t="s">
+        <v>677</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>678</v>
+      </c>
+      <c r="C2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>680</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>681</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{DBE23AF4-F5A4-459B-B645-EA5587742E1C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:M997"/>
   <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -24885,1163 +26177,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:M997"/>
-  <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="6" width="20.4609375" customWidth="1"/>
-    <col min="7" max="13" width="43.3046875" customWidth="1"/>
-    <col min="16384" max="16384" width="11.4609375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" s="42" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="51" t="s">
-        <v>300</v>
-      </c>
-      <c r="C1" s="52" t="s">
-        <v>301</v>
-      </c>
-      <c r="D1" s="53" t="s">
-        <v>302</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>303</v>
-      </c>
-      <c r="F1" s="52" t="s">
-        <v>304</v>
-      </c>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-    </row>
-    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="54"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-    </row>
-    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="56"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-    </row>
-    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-    </row>
-    <row r="5" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-    </row>
-    <row r="6" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="56"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-    </row>
-    <row r="7" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="56"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-    </row>
-    <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="56"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-    </row>
-    <row r="9" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="40"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{649E6E49-1C43-4DBC-A22C-62A99DEF1F6A}">
-      <formula1>INDIRECT("study[studyId]")</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/Templates/MIAPPE_Spreadsheet_Template.xlsx
+++ b/Templates/MIAPPE_Spreadsheet_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\MIAPPE\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C83358-2032-4458-95BE-E8D2655F1635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8704DE-36BD-45DC-94E5-6E0416144695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="891" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="691">
   <si>
     <t>README</t>
   </si>
@@ -2292,6 +2292,24 @@
   <si>
     <t>N</t>
   </si>
+  <si>
+    <t>expeFactorLevelId</t>
+  </si>
+  <si>
+    <t>expeFactorLevel</t>
+  </si>
+  <si>
+    <t>expeFactorLevelAccession</t>
+  </si>
+  <si>
+    <t>expeFactorLevelDesc</t>
+  </si>
+  <si>
+    <t>S1-N</t>
+  </si>
+  <si>
+    <t>N1</t>
+  </si>
 </sst>
 </file>
 
@@ -2300,7 +2318,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2486,6 +2504,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006AB9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2545,7 +2569,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2714,6 +2738,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5338,6 +5363,22 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:G2" insertRow="1" totalsRowShown="0" dataDxfId="32">
+  <autoFilter ref="A1:G2" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="33"/>
+  </tableColumns>
+  <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="23" dataDxfId="24">
   <autoFilter ref="A1:G2" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}"/>
   <tableColumns count="7">
@@ -5353,7 +5394,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:Q2" insertRow="1" totalsRowShown="0" dataDxfId="5">
   <autoFilter ref="A1:Q2" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}"/>
   <tableColumns count="17">
@@ -5379,7 +5420,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}" name="environmentParameters" displayName="environmentParameters" ref="A1:C3" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="A1:C3" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}"/>
   <tableColumns count="3">
@@ -5511,6 +5552,22 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{C9BF05A2-1ABB-4D33-BC15-C5E51AF45999}" name="experimentFactorLevel" displayName="experimentFactorLevel" ref="A1:E2" totalsRowShown="0">
+  <autoFilter ref="A1:E2" xr:uid="{C9BF05A2-1ABB-4D33-BC15-C5E51AF45999}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{87ACD6F9-EF3B-4A5E-B872-92E772B18A0D}" name="expeFactorId"/>
+    <tableColumn id="2" xr3:uid="{684FB454-4CC5-45F7-9C3C-B04475EADF64}" name="expeFactorLevelId">
+      <calculatedColumnFormula>CONCATENATE(experimentFactorLevel[expeFactorId],"-",experimentFactorLevel[expeFactorLevel])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{1C4A38F3-CA10-4B27-8557-5CEB94A37762}" name="expeFactorLevel"/>
+    <tableColumn id="4" xr3:uid="{8AD64F88-1111-477C-8058-D8790CFA7C77}" name="expeFactorLevelAccession"/>
+    <tableColumn id="5" xr3:uid="{925EFD52-D576-4B2F-BE3D-7FEE62D537D8}" name="expeFactorLevelDesc"/>
+  </tableColumns>
+  <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:F2" insertRow="1" totalsRowShown="0" dataDxfId="40">
   <autoFilter ref="A1:F2" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}"/>
   <tableColumns count="6">
@@ -5520,22 +5577,6 @@
     <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="43"/>
     <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="42"/>
     <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="41"/>
-  </tableColumns>
-  <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:G2" insertRow="1" totalsRowShown="0" dataDxfId="32">
-  <autoFilter ref="A1:G2" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -24321,9 +24362,57 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0E16F6-2188-4422-AF91-E595A36EE21A}">
-  <dimension ref="A1"/>
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.07421875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.53515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.07421875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>685</v>
+      </c>
+      <c r="C1" t="s">
+        <v>686</v>
+      </c>
+      <c r="D1" t="s">
+        <v>687</v>
+      </c>
+      <c r="E1" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B2" t="str">
+        <f>CONCATENATE(experimentFactorLevel[expeFactorId],"-",experimentFactorLevel[expeFactorLevel])</f>
+        <v>S1-N-N1</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>690</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{BB15239E-DF5D-4524-AED3-F9F9639D5B2D}">
+      <formula1>INDIRECT("experimentalFactor[expeFactorId]")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Templates/MIAPPE_Spreadsheet_Template.xlsx
+++ b/Templates/MIAPPE_Spreadsheet_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\MIAPPE\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8704DE-36BD-45DC-94E5-6E0416144695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDA4427-A835-4119-9894-C17474B04E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="891" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="891" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="697">
   <si>
     <t>README</t>
   </si>
@@ -2296,9 +2296,6 @@
     <t>expeFactorLevelId</t>
   </si>
   <si>
-    <t>expeFactorLevel</t>
-  </si>
-  <si>
     <t>expeFactorLevelAccession</t>
   </si>
   <si>
@@ -2309,6 +2306,27 @@
   </si>
   <si>
     <t>N1</t>
+  </si>
+  <si>
+    <t>expeFactorLevelCode</t>
+  </si>
+  <si>
+    <t>variableAccession</t>
+  </si>
+  <si>
+    <t>traitEntityAccession</t>
+  </si>
+  <si>
+    <t>traitCharacteristicAccession</t>
+  </si>
+  <si>
+    <t>traitAccession</t>
+  </si>
+  <si>
+    <t>methodAccession</t>
+  </si>
+  <si>
+    <t>scaleAccession</t>
   </si>
 </sst>
 </file>
@@ -2747,6 +2765,26 @@
   <dxfs count="134">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -3062,26 +3100,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5395,33 +5413,33 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:Q2" insertRow="1" totalsRowShown="0" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:Q2" insertRow="1" totalsRowShown="0" dataDxfId="6">
   <autoFilter ref="A1:Q2" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccNumber" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccession" dataDxfId="19"/>
     <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccessionNumber" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccessionNumber" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccNumber" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccNumber" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="8"/>
-    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccNumber" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="timeScale" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccession" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccession" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccession" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccession" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="9"/>
+    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccession" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="timeScale" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}" name="environmentParameters" displayName="environmentParameters" ref="A1:C3" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}" name="environmentParameters" displayName="environmentParameters" ref="A1:C3" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:C3" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{5E761B2A-3F92-4181-AF5D-F423F0564A09}" name="envParam"/>
@@ -5437,7 +5455,7 @@
   <autoFilter ref="A1:T3" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="114"/>
-    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="parentStudyId" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="parentStudyId" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="113"/>
     <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="112"/>
     <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="111"/>
@@ -5539,13 +5557,13 @@
   <autoFilter ref="A1:F2" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{8AF0BF35-BAC4-4E9A-A1CC-B83DC7399496}" name="expeFactorCode" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{67BFB12E-F4AF-4C45-B7B6-4791A656C30A}" name="expeFactorId" dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{8AF0BF35-BAC4-4E9A-A1CC-B83DC7399496}" name="expeFactorCode" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{67BFB12E-F4AF-4C45-B7B6-4791A656C30A}" name="expeFactorId" dataDxfId="3">
       <calculatedColumnFormula>CONCATENATE(experimentalFactor[studyId],"-",experimentalFactor[expeFactorCode])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="49"/>
     <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5557,9 +5575,9 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{87ACD6F9-EF3B-4A5E-B872-92E772B18A0D}" name="expeFactorId"/>
     <tableColumn id="2" xr3:uid="{684FB454-4CC5-45F7-9C3C-B04475EADF64}" name="expeFactorLevelId">
-      <calculatedColumnFormula>CONCATENATE(experimentFactorLevel[expeFactorId],"-",experimentFactorLevel[expeFactorLevel])</calculatedColumnFormula>
+      <calculatedColumnFormula>CONCATENATE(experimentFactorLevel[expeFactorId],"-",experimentFactorLevel[expeFactorLevelCode])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1C4A38F3-CA10-4B27-8557-5CEB94A37762}" name="expeFactorLevel"/>
+    <tableColumn id="3" xr3:uid="{1C4A38F3-CA10-4B27-8557-5CEB94A37762}" name="expeFactorLevelCode"/>
     <tableColumn id="4" xr3:uid="{8AD64F88-1111-477C-8058-D8790CFA7C77}" name="expeFactorLevelAccession"/>
     <tableColumn id="5" xr3:uid="{925EFD52-D576-4B2F-BE3D-7FEE62D537D8}" name="expeFactorLevelDesc"/>
   </tableColumns>
@@ -13584,8 +13602,8 @@
     <col min="2" max="2" width="11.4609375" customWidth="1"/>
     <col min="3" max="3" width="14.84375" customWidth="1"/>
     <col min="4" max="4" width="19.69140625" customWidth="1"/>
-    <col min="5" max="5" width="11.15234375" customWidth="1"/>
-    <col min="6" max="6" width="10.921875" customWidth="1"/>
+    <col min="5" max="5" width="14.765625" customWidth="1"/>
+    <col min="6" max="6" width="13.69140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.15234375" customWidth="1"/>
     <col min="8" max="8" width="17.921875" customWidth="1"/>
     <col min="9" max="9" width="33.15234375" customWidth="1"/>
@@ -13612,7 +13630,7 @@
         <v>389</v>
       </c>
       <c r="D1" s="59" t="s">
-        <v>390</v>
+        <v>691</v>
       </c>
       <c r="E1" s="57" t="s">
         <v>391</v>
@@ -13621,22 +13639,22 @@
         <v>392</v>
       </c>
       <c r="G1" s="59" t="s">
-        <v>393</v>
+        <v>692</v>
       </c>
       <c r="H1" s="59" t="s">
         <v>394</v>
       </c>
       <c r="I1" s="59" t="s">
-        <v>395</v>
+        <v>693</v>
       </c>
       <c r="J1" s="59" t="s">
-        <v>396</v>
+        <v>694</v>
       </c>
       <c r="K1" s="57" t="s">
         <v>397</v>
       </c>
       <c r="L1" s="59" t="s">
-        <v>398</v>
+        <v>695</v>
       </c>
       <c r="M1" s="58" t="s">
         <v>399</v>
@@ -13648,7 +13666,7 @@
         <v>401</v>
       </c>
       <c r="P1" s="59" t="s">
-        <v>402</v>
+        <v>696</v>
       </c>
       <c r="Q1" s="59" t="s">
         <v>403</v>
@@ -24370,8 +24388,8 @@
   <cols>
     <col min="1" max="1" width="14.07421875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.4609375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.53515625" customWidth="1"/>
     <col min="5" max="5" width="21.07421875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -24382,26 +24400,26 @@
       <c r="B1" s="68" t="s">
         <v>685</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="63" t="s">
+        <v>690</v>
+      </c>
+      <c r="D1" t="s">
         <v>686</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>687</v>
-      </c>
-      <c r="E1" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B2" t="str">
+        <f>CONCATENATE(experimentFactorLevel[expeFactorId],"-",experimentFactorLevel[expeFactorLevelCode])</f>
+        <v>S1-N-N1</v>
+      </c>
+      <c r="C2" s="63" t="s">
         <v>689</v>
-      </c>
-      <c r="B2" t="str">
-        <f>CONCATENATE(experimentFactorLevel[expeFactorId],"-",experimentFactorLevel[expeFactorLevel])</f>
-        <v>S1-N-N1</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>690</v>
       </c>
     </row>
   </sheetData>

--- a/Templates/MIAPPE_Spreadsheet_Template.xlsx
+++ b/Templates/MIAPPE_Spreadsheet_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\MIAPPE\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDA4427-A835-4119-9894-C17474B04E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08564F4-4A13-4326-8E07-228211CF19C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="891" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="29040" windowHeight="16440" tabRatio="891" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="701">
   <si>
     <t>README</t>
   </si>
@@ -2327,6 +2327,18 @@
   </si>
   <si>
     <t>scaleAccession</t>
+  </si>
+  <si>
+    <t>participant</t>
+  </si>
+  <si>
+    <t>participantAccession</t>
+  </si>
+  <si>
+    <t>participantRole</t>
+  </si>
+  <si>
+    <t>participantRoleAccession</t>
   </si>
 </sst>
 </file>
@@ -2762,7 +2774,87 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="138">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5341,15 +5433,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="MiappeStyle" pivot="0" count="9" xr9:uid="{59C54380-D204-4007-9CC6-0890CCDEE3C9}">
-      <tableStyleElement type="wholeTable" dxfId="133"/>
-      <tableStyleElement type="headerRow" dxfId="132"/>
-      <tableStyleElement type="totalRow" dxfId="131"/>
-      <tableStyleElement type="firstColumn" dxfId="130"/>
-      <tableStyleElement type="lastColumn" dxfId="129"/>
-      <tableStyleElement type="firstRowStripe" dxfId="128"/>
-      <tableStyleElement type="secondRowStripe" dxfId="127"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="126"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="125"/>
+      <tableStyleElement type="wholeTable" dxfId="137"/>
+      <tableStyleElement type="headerRow" dxfId="136"/>
+      <tableStyleElement type="totalRow" dxfId="135"/>
+      <tableStyleElement type="firstColumn" dxfId="134"/>
+      <tableStyleElement type="lastColumn" dxfId="133"/>
+      <tableStyleElement type="firstRowStripe" dxfId="132"/>
+      <tableStyleElement type="secondRowStripe" dxfId="131"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="130"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="129"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5364,82 +5456,86 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}" name="investigation" displayName="investigation" ref="A1:H2" totalsRowShown="0" headerRowDxfId="115" dataDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}" name="investigation" displayName="investigation" ref="A1:H2" totalsRowShown="0" headerRowDxfId="119" dataDxfId="120">
   <autoFilter ref="A1:H2" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{25F01F79-3E24-44AF-B5E3-4EB20FD9A360}" name="investigationId" dataDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{16E59F0F-AC6D-4504-A428-E7D7AC601401}" name="investigationTitle" dataDxfId="123"/>
-    <tableColumn id="3" xr3:uid="{4668A34F-CEFF-43A7-84AA-B014E3A90F47}" name="investigationDescription" dataDxfId="122"/>
-    <tableColumn id="4" xr3:uid="{403353FA-EBA5-418F-8273-81472CDF29D4}" name="submissionDate" dataDxfId="121"/>
-    <tableColumn id="5" xr3:uid="{18E43DB3-511F-4E0E-B357-B4A6E40F0660}" name="publicReleaseDate" dataDxfId="120"/>
-    <tableColumn id="6" xr3:uid="{91C01C8C-69AF-4B74-BA16-1C962EDAF32D}" name="license" dataDxfId="119"/>
-    <tableColumn id="7" xr3:uid="{E94BB99A-781A-4442-AD9C-7E4D99028DC9}" name="miappeVersion" dataDxfId="118"/>
-    <tableColumn id="8" xr3:uid="{91B9E445-65BD-412A-95C1-EA371F946FCA}" name="associatedPublication" dataDxfId="117"/>
+    <tableColumn id="1" xr3:uid="{25F01F79-3E24-44AF-B5E3-4EB20FD9A360}" name="investigationId" dataDxfId="128"/>
+    <tableColumn id="2" xr3:uid="{16E59F0F-AC6D-4504-A428-E7D7AC601401}" name="investigationTitle" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{4668A34F-CEFF-43A7-84AA-B014E3A90F47}" name="investigationDescription" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{403353FA-EBA5-418F-8273-81472CDF29D4}" name="submissionDate" dataDxfId="125"/>
+    <tableColumn id="5" xr3:uid="{18E43DB3-511F-4E0E-B357-B4A6E40F0660}" name="publicReleaseDate" dataDxfId="124"/>
+    <tableColumn id="6" xr3:uid="{91C01C8C-69AF-4B74-BA16-1C962EDAF32D}" name="license" dataDxfId="123"/>
+    <tableColumn id="7" xr3:uid="{E94BB99A-781A-4442-AD9C-7E4D99028DC9}" name="miappeVersion" dataDxfId="122"/>
+    <tableColumn id="8" xr3:uid="{91B9E445-65BD-412A-95C1-EA371F946FCA}" name="associatedPublication" dataDxfId="121"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:G2" insertRow="1" totalsRowShown="0" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:G2" insertRow="1" totalsRowShown="0" dataDxfId="36">
   <autoFilter ref="A1:G2" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="23" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="27" dataDxfId="28">
   <autoFilter ref="A1:G2" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{92A1E618-2F85-46E4-B7EF-76ED045C215B}" name="obsUnitId" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{A0DFEC37-340B-4DF8-907B-A9769602FD28}" name="sampleId" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{D455AF29-BE41-4DDA-A9B2-A46F4EEA6767}" name="developmentStage" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{C24109D3-E8A6-4810-A0A6-ACD6730F0D08}" name="anatomicalEntity" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{5C630D57-B424-4325-BC0C-BEEBEDC89DBB}" name="sampleDesc" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{CDEC6C64-2387-4FCF-9A2C-63F54020D0A0}" name="collectionDate" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{FFB2A4F7-3C7D-4BC5-AD9E-C14C20349305}" name="externalId" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{92A1E618-2F85-46E4-B7EF-76ED045C215B}" name="obsUnitId" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{A0DFEC37-340B-4DF8-907B-A9769602FD28}" name="sampleId" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{D455AF29-BE41-4DDA-A9B2-A46F4EEA6767}" name="developmentStage" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{C24109D3-E8A6-4810-A0A6-ACD6730F0D08}" name="anatomicalEntity" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{5C630D57-B424-4325-BC0C-BEEBEDC89DBB}" name="sampleDesc" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{CDEC6C64-2387-4FCF-9A2C-63F54020D0A0}" name="collectionDate" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{FFB2A4F7-3C7D-4BC5-AD9E-C14C20349305}" name="externalId" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:Q2" insertRow="1" totalsRowShown="0" dataDxfId="6">
-  <autoFilter ref="A1:Q2" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}"/>
-  <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccession" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccession" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccession" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccession" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccession" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="9"/>
-    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccession" dataDxfId="8"/>
-    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="timeScale" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:U2" insertRow="1" totalsRowShown="0" dataDxfId="10">
+  <autoFilter ref="A1:U2" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccession" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccession" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccession" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccession" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccession" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccession" dataDxfId="12"/>
+    <tableColumn id="19" xr3:uid="{EE91A801-8376-4314-ADFB-6E32C3AE8AE4}" name="timeScale" dataDxfId="3"/>
+    <tableColumn id="22" xr3:uid="{A52D8785-E3B2-4548-AA8A-0964285F0DB9}" name="participant" dataDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{CA21FA4C-5A61-4852-9BA7-6FDDF22D4ADC}" name="participantAccession" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{3DF54E16-A553-4C7E-9762-C6517F5AD994}" name="participantRole" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="participantRoleAccession" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}" name="environmentParameters" displayName="environmentParameters" ref="A1:C3" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}" name="environmentParameters" displayName="environmentParameters" ref="A1:C3" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A1:C3" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{5E761B2A-3F92-4181-AF5D-F423F0564A09}" name="envParam"/>
@@ -5451,119 +5547,119 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:T3" totalsRowShown="0" dataDxfId="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:T3" totalsRowShown="0" dataDxfId="99">
   <autoFilter ref="A1:T3" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="114"/>
-    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="parentStudyId" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="113"/>
-    <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="112"/>
-    <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="111"/>
-    <tableColumn id="5" xr3:uid="{E557DB42-3379-4598-AAF9-21798BC64DAB}" name="studyEndDate" dataDxfId="110"/>
-    <tableColumn id="6" xr3:uid="{1EEA2EC5-CA19-40B4-9DFB-2DE9A9E916EA}" name="contactInst" dataDxfId="109"/>
-    <tableColumn id="7" xr3:uid="{E0A5C222-CFE5-4E9C-8E84-0892043DBD21}" name="locationCountry" dataDxfId="108"/>
-    <tableColumn id="8" xr3:uid="{7B635D2A-56C5-48B0-A880-E33ADE030AB1}" name="siteName" dataDxfId="107"/>
-    <tableColumn id="9" xr3:uid="{2F8227C3-F11C-4DAA-93EB-CEBD94FF81A9}" name="locationLatitude" dataDxfId="106"/>
-    <tableColumn id="10" xr3:uid="{6A14EB46-0BF4-45C6-9048-E1B7D13E633A}" name="locationLongitude" dataDxfId="105"/>
-    <tableColumn id="11" xr3:uid="{9954429A-AA41-408C-BB04-D73EDB89D73F}" name="locationAltitude" dataDxfId="104"/>
-    <tableColumn id="12" xr3:uid="{39FEDA43-D994-4742-B319-3DFED43EF79B}" name="expeDesignDesc" dataDxfId="103"/>
-    <tableColumn id="13" xr3:uid="{C9F6A881-1CF1-4AD9-8305-B7E26FD78E3B}" name="expeDesignType" dataDxfId="102"/>
-    <tableColumn id="14" xr3:uid="{253A58C7-1A2A-4D25-9622-3AE33F89A685}" name="obsUnitLevelHierarchy" dataDxfId="101"/>
-    <tableColumn id="15" xr3:uid="{10DCEB5F-0BF5-4476-83E5-B973A516A8CD}" name="obsUnitDesc" dataDxfId="100"/>
-    <tableColumn id="16" xr3:uid="{0D36E7FE-2245-4B79-9A59-4C64590731A5}" name="growthFacilityDesc" dataDxfId="99"/>
-    <tableColumn id="17" xr3:uid="{599307E8-6E88-4D3F-BF48-ADF70D109D18}" name="growthFacilityType" dataDxfId="98"/>
-    <tableColumn id="18" xr3:uid="{63403E81-283C-4E2E-984D-9EFC0886E90C}" name="culturalPractice" dataDxfId="97"/>
-    <tableColumn id="19" xr3:uid="{E74D4B3A-67BC-482F-8485-FC7D9088A8B6}" name="expeDesignMap" dataDxfId="96"/>
+    <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="118"/>
+    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="parentStudyId" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="117"/>
+    <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="116"/>
+    <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="115"/>
+    <tableColumn id="5" xr3:uid="{E557DB42-3379-4598-AAF9-21798BC64DAB}" name="studyEndDate" dataDxfId="114"/>
+    <tableColumn id="6" xr3:uid="{1EEA2EC5-CA19-40B4-9DFB-2DE9A9E916EA}" name="contactInst" dataDxfId="113"/>
+    <tableColumn id="7" xr3:uid="{E0A5C222-CFE5-4E9C-8E84-0892043DBD21}" name="locationCountry" dataDxfId="112"/>
+    <tableColumn id="8" xr3:uid="{7B635D2A-56C5-48B0-A880-E33ADE030AB1}" name="siteName" dataDxfId="111"/>
+    <tableColumn id="9" xr3:uid="{2F8227C3-F11C-4DAA-93EB-CEBD94FF81A9}" name="locationLatitude" dataDxfId="110"/>
+    <tableColumn id="10" xr3:uid="{6A14EB46-0BF4-45C6-9048-E1B7D13E633A}" name="locationLongitude" dataDxfId="109"/>
+    <tableColumn id="11" xr3:uid="{9954429A-AA41-408C-BB04-D73EDB89D73F}" name="locationAltitude" dataDxfId="108"/>
+    <tableColumn id="12" xr3:uid="{39FEDA43-D994-4742-B319-3DFED43EF79B}" name="expeDesignDesc" dataDxfId="107"/>
+    <tableColumn id="13" xr3:uid="{C9F6A881-1CF1-4AD9-8305-B7E26FD78E3B}" name="expeDesignType" dataDxfId="106"/>
+    <tableColumn id="14" xr3:uid="{253A58C7-1A2A-4D25-9622-3AE33F89A685}" name="obsUnitLevelHierarchy" dataDxfId="105"/>
+    <tableColumn id="15" xr3:uid="{10DCEB5F-0BF5-4476-83E5-B973A516A8CD}" name="obsUnitDesc" dataDxfId="104"/>
+    <tableColumn id="16" xr3:uid="{0D36E7FE-2245-4B79-9A59-4C64590731A5}" name="growthFacilityDesc" dataDxfId="103"/>
+    <tableColumn id="17" xr3:uid="{599307E8-6E88-4D3F-BF48-ADF70D109D18}" name="growthFacilityType" dataDxfId="102"/>
+    <tableColumn id="18" xr3:uid="{63403E81-283C-4E2E-984D-9EFC0886E90C}" name="culturalPractice" dataDxfId="101"/>
+    <tableColumn id="19" xr3:uid="{E74D4B3A-67BC-482F-8485-FC7D9088A8B6}" name="expeDesignMap" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}" name="person" displayName="person" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="87" dataDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}" name="person" displayName="person" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="91" dataDxfId="92">
   <autoFilter ref="A1:F2" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{49A703DB-336A-4F60-9DA6-8249763A2765}" name="studyId" dataDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{65039BF4-A122-4B88-8EB2-FD3ED61B8912}" name="personName" dataDxfId="93"/>
-    <tableColumn id="3" xr3:uid="{4B7588A4-B756-4E28-B8A4-AFB8D62031B4}" name="personEmail" dataDxfId="92"/>
-    <tableColumn id="4" xr3:uid="{639FC837-B543-4A62-B2C2-3EE761EF5EF7}" name="personId" dataDxfId="91"/>
-    <tableColumn id="5" xr3:uid="{593F31A8-CDAA-47CF-89F3-2902C6B8D3C8}" name="personRole" dataDxfId="90"/>
-    <tableColumn id="6" xr3:uid="{5FCF059F-31D5-4218-8D81-DC379C42EAF4}" name="personAffiliation" dataDxfId="89"/>
+    <tableColumn id="1" xr3:uid="{49A703DB-336A-4F60-9DA6-8249763A2765}" name="studyId" dataDxfId="98"/>
+    <tableColumn id="2" xr3:uid="{65039BF4-A122-4B88-8EB2-FD3ED61B8912}" name="personName" dataDxfId="97"/>
+    <tableColumn id="3" xr3:uid="{4B7588A4-B756-4E28-B8A4-AFB8D62031B4}" name="personEmail" dataDxfId="96"/>
+    <tableColumn id="4" xr3:uid="{639FC837-B543-4A62-B2C2-3EE761EF5EF7}" name="personId" dataDxfId="95"/>
+    <tableColumn id="5" xr3:uid="{593F31A8-CDAA-47CF-89F3-2902C6B8D3C8}" name="personRole" dataDxfId="94"/>
+    <tableColumn id="6" xr3:uid="{5FCF059F-31D5-4218-8D81-DC379C42EAF4}" name="personAffiliation" dataDxfId="93"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}" name="dataFile" displayName="dataFile" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="81" dataDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}" name="dataFile" displayName="dataFile" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="85" dataDxfId="86">
   <autoFilter ref="A1:D2" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AD6A7B95-2E4C-4264-86B4-35031C8932E3}" name="studyId" dataDxfId="86"/>
-    <tableColumn id="2" xr3:uid="{A5C92CF7-B78F-4910-A250-8A16D6E7889C}" name="dataFileLink" dataDxfId="85"/>
-    <tableColumn id="3" xr3:uid="{620AC217-74DA-496A-9696-16EF7D98E86C}" name="dataFileDesc" dataDxfId="84"/>
-    <tableColumn id="4" xr3:uid="{79F128D7-FDA0-4F62-B04B-DAEE7E495850}" name="dataFileVersion" dataDxfId="83"/>
+    <tableColumn id="1" xr3:uid="{AD6A7B95-2E4C-4264-86B4-35031C8932E3}" name="studyId" dataDxfId="90"/>
+    <tableColumn id="2" xr3:uid="{A5C92CF7-B78F-4910-A250-8A16D6E7889C}" name="dataFileLink" dataDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{620AC217-74DA-496A-9696-16EF7D98E86C}" name="dataFileDesc" dataDxfId="88"/>
+    <tableColumn id="4" xr3:uid="{79F128D7-FDA0-4F62-B04B-DAEE7E495850}" name="dataFileVersion" dataDxfId="87"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}" name="biologicalMaterial" displayName="biologicalMaterial" ref="A1:X2" insertRow="1" totalsRowShown="0" headerRowDxfId="55" dataDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}" name="biologicalMaterial" displayName="biologicalMaterial" ref="A1:X2" insertRow="1" totalsRowShown="0" headerRowDxfId="59" dataDxfId="60">
   <autoFilter ref="A1:X2" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}"/>
   <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{71E6992E-3AF7-4C8A-9C1E-930C105005E2}" name="studyId" dataDxfId="80"/>
-    <tableColumn id="2" xr3:uid="{BA8B45A2-9F79-4EE6-A38F-EF56D5CE4A1A}" name="biologicalMaterialId" dataDxfId="79"/>
-    <tableColumn id="3" xr3:uid="{546FEA19-FA9D-47D3-BF6E-57CDA029B0A3}" name="biologicalMaterialExtId" dataDxfId="78"/>
-    <tableColumn id="4" xr3:uid="{0DD21880-A5E2-4076-AA9F-554DE7C7E0D1}" name="organism" dataDxfId="77"/>
-    <tableColumn id="5" xr3:uid="{9760C8F1-7162-4A84-80C2-FBEC779AFAD0}" name="genus" dataDxfId="76"/>
-    <tableColumn id="6" xr3:uid="{D7026284-DE40-4B04-A583-983A0B5FB5BB}" name="species" dataDxfId="75"/>
-    <tableColumn id="7" xr3:uid="{22046373-BBD5-4919-AC4C-AA8E91D97026}" name="infraspecificName" dataDxfId="74"/>
-    <tableColumn id="8" xr3:uid="{579B0DCA-BD9C-4E7B-BB3B-3FB19A4CBCA3}" name="biologicalMaterialLatitude" dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{A7E064AC-CDCF-4898-BEF3-07CF88887A4E}" name="biologicalMaterialLongitude" dataDxfId="72"/>
-    <tableColumn id="10" xr3:uid="{D55DD07C-0BE6-4D7D-80E1-B7195245711A}" name="biologicalMaterialAltitude" dataDxfId="71"/>
-    <tableColumn id="11" xr3:uid="{CA82A017-8E46-417C-9A1F-D7010C7B489F}" name="biologicalMaterialCoordUncertainty" dataDxfId="70"/>
-    <tableColumn id="12" xr3:uid="{16F6B082-1241-4094-AFDC-6E6F5B63F502}" name="biologicalMaterialPreprocessing" dataDxfId="69"/>
-    <tableColumn id="13" xr3:uid="{16F5564F-9F1B-4CEB-8DEC-4F46E89C2EB5}" name="materialSourceId" dataDxfId="68"/>
-    <tableColumn id="14" xr3:uid="{0AB5DA63-1709-41B8-9FAD-5B1A8A45E649}" name="materialSourceDoi" dataDxfId="67"/>
-    <tableColumn id="15" xr3:uid="{26116E4A-CA0A-4D6C-A863-AEA24B0E0C24}" name="materialSourceAccNumber" dataDxfId="66"/>
-    <tableColumn id="16" xr3:uid="{0C2E647E-5127-470F-859E-ED727EEFA3B9}" name="materialSourceAccName" dataDxfId="65"/>
-    <tableColumn id="17" xr3:uid="{B6097563-29EF-4C10-9096-04A2C164B15A}" name="materialSourceInstCode" dataDxfId="64"/>
-    <tableColumn id="18" xr3:uid="{BEA38246-EAA3-4450-B29F-D608607C2513}" name="materialSourceInstName" dataDxfId="63"/>
-    <tableColumn id="19" xr3:uid="{E8257013-CD5D-4534-9CD0-08D9EBBE7EF0}" name="materialSourceOtherIds" dataDxfId="62"/>
-    <tableColumn id="20" xr3:uid="{BE0E6D94-2ED0-4863-9DE5-9AA6BD4643D6}" name="materialSourceLatitude" dataDxfId="61"/>
-    <tableColumn id="21" xr3:uid="{BD849876-C99C-4475-87D4-DEECBE575F67}" name="materialSourceLongitude" dataDxfId="60"/>
-    <tableColumn id="22" xr3:uid="{0C871681-B897-43DD-A6BE-F03CAA6574F6}" name="materialSourceAltitude" dataDxfId="59"/>
-    <tableColumn id="23" xr3:uid="{ECC67BD8-3E1F-4A97-95B0-A9CCE07839CA}" name="materialSourceCoordUncertainty" dataDxfId="58"/>
-    <tableColumn id="24" xr3:uid="{C66E78D2-DB97-4D59-8D52-ECE79ED6BB86}" name="materialSourceDesc" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{71E6992E-3AF7-4C8A-9C1E-930C105005E2}" name="studyId" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{BA8B45A2-9F79-4EE6-A38F-EF56D5CE4A1A}" name="biologicalMaterialId" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{546FEA19-FA9D-47D3-BF6E-57CDA029B0A3}" name="biologicalMaterialExtId" dataDxfId="82"/>
+    <tableColumn id="4" xr3:uid="{0DD21880-A5E2-4076-AA9F-554DE7C7E0D1}" name="organism" dataDxfId="81"/>
+    <tableColumn id="5" xr3:uid="{9760C8F1-7162-4A84-80C2-FBEC779AFAD0}" name="genus" dataDxfId="80"/>
+    <tableColumn id="6" xr3:uid="{D7026284-DE40-4B04-A583-983A0B5FB5BB}" name="species" dataDxfId="79"/>
+    <tableColumn id="7" xr3:uid="{22046373-BBD5-4919-AC4C-AA8E91D97026}" name="infraspecificName" dataDxfId="78"/>
+    <tableColumn id="8" xr3:uid="{579B0DCA-BD9C-4E7B-BB3B-3FB19A4CBCA3}" name="biologicalMaterialLatitude" dataDxfId="77"/>
+    <tableColumn id="9" xr3:uid="{A7E064AC-CDCF-4898-BEF3-07CF88887A4E}" name="biologicalMaterialLongitude" dataDxfId="76"/>
+    <tableColumn id="10" xr3:uid="{D55DD07C-0BE6-4D7D-80E1-B7195245711A}" name="biologicalMaterialAltitude" dataDxfId="75"/>
+    <tableColumn id="11" xr3:uid="{CA82A017-8E46-417C-9A1F-D7010C7B489F}" name="biologicalMaterialCoordUncertainty" dataDxfId="74"/>
+    <tableColumn id="12" xr3:uid="{16F6B082-1241-4094-AFDC-6E6F5B63F502}" name="biologicalMaterialPreprocessing" dataDxfId="73"/>
+    <tableColumn id="13" xr3:uid="{16F5564F-9F1B-4CEB-8DEC-4F46E89C2EB5}" name="materialSourceId" dataDxfId="72"/>
+    <tableColumn id="14" xr3:uid="{0AB5DA63-1709-41B8-9FAD-5B1A8A45E649}" name="materialSourceDoi" dataDxfId="71"/>
+    <tableColumn id="15" xr3:uid="{26116E4A-CA0A-4D6C-A863-AEA24B0E0C24}" name="materialSourceAccNumber" dataDxfId="70"/>
+    <tableColumn id="16" xr3:uid="{0C2E647E-5127-470F-859E-ED727EEFA3B9}" name="materialSourceAccName" dataDxfId="69"/>
+    <tableColumn id="17" xr3:uid="{B6097563-29EF-4C10-9096-04A2C164B15A}" name="materialSourceInstCode" dataDxfId="68"/>
+    <tableColumn id="18" xr3:uid="{BEA38246-EAA3-4450-B29F-D608607C2513}" name="materialSourceInstName" dataDxfId="67"/>
+    <tableColumn id="19" xr3:uid="{E8257013-CD5D-4534-9CD0-08D9EBBE7EF0}" name="materialSourceOtherIds" dataDxfId="66"/>
+    <tableColumn id="20" xr3:uid="{BE0E6D94-2ED0-4863-9DE5-9AA6BD4643D6}" name="materialSourceLatitude" dataDxfId="65"/>
+    <tableColumn id="21" xr3:uid="{BD849876-C99C-4475-87D4-DEECBE575F67}" name="materialSourceLongitude" dataDxfId="64"/>
+    <tableColumn id="22" xr3:uid="{0C871681-B897-43DD-A6BE-F03CAA6574F6}" name="materialSourceAltitude" dataDxfId="63"/>
+    <tableColumn id="23" xr3:uid="{ECC67BD8-3E1F-4A97-95B0-A9CCE07839CA}" name="materialSourceCoordUncertainty" dataDxfId="62"/>
+    <tableColumn id="24" xr3:uid="{C66E78D2-DB97-4D59-8D52-ECE79ED6BB86}" name="materialSourceDesc" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}" name="environment" displayName="environment" ref="A1:C2" insertRow="1" totalsRowShown="0" headerRowDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}" name="environment" displayName="environment" ref="A1:C2" insertRow="1" totalsRowShown="0" headerRowDxfId="55">
   <autoFilter ref="A1:C2" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{08C0BD82-D970-44E6-99E3-B4872FECEFE5}" name="studyId" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{F9DC7CC5-88B3-4A9A-B462-9FB971836B81}" name="envParam" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{65E72A00-3C03-4A17-922C-EE6A4A3D8D80}" name="envParamValue" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{08C0BD82-D970-44E6-99E3-B4872FECEFE5}" name="studyId" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{F9DC7CC5-88B3-4A9A-B462-9FB971836B81}" name="envParam" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{65E72A00-3C03-4A17-922C-EE6A4A3D8D80}" name="envParamValue" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}" name="experimentalFactor" displayName="experimentalFactor" ref="A1:F2" totalsRowShown="0" headerRowDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}" name="experimentalFactor" displayName="experimentalFactor" ref="A1:F2" totalsRowShown="0" headerRowDxfId="51">
   <autoFilter ref="A1:F2" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{8AF0BF35-BAC4-4E9A-A1CC-B83DC7399496}" name="expeFactorCode" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{67BFB12E-F4AF-4C45-B7B6-4791A656C30A}" name="expeFactorId" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{8AF0BF35-BAC4-4E9A-A1CC-B83DC7399496}" name="expeFactorCode" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{67BFB12E-F4AF-4C45-B7B6-4791A656C30A}" name="expeFactorId" dataDxfId="7">
       <calculatedColumnFormula>CONCATENATE(experimentalFactor[studyId],"-",experimentalFactor[expeFactorCode])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5586,15 +5682,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:F2" insertRow="1" totalsRowShown="0" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:F2" insertRow="1" totalsRowShown="0" dataDxfId="44">
   <autoFilter ref="A1:F2" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{DB25986C-BD6F-40F9-A226-C9A11BBDF460}" name="studyId" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{6EE72788-DEAD-4FC0-9383-C6415EC5E8A5}" name="obsUnitId" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{0DDCD5FF-AC45-4794-9B28-BBD982C1FB84}" name="eventType" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{DB25986C-BD6F-40F9-A226-C9A11BBDF460}" name="studyId" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{6EE72788-DEAD-4FC0-9383-C6415EC5E8A5}" name="obsUnitId" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{0DDCD5FF-AC45-4794-9B28-BBD982C1FB84}" name="eventType" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13595,7 +13691,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:Q997"/>
+  <dimension ref="A1:U997"/>
   <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.921875" customWidth="1"/>
@@ -13613,13 +13709,15 @@
     <col min="13" max="13" width="13.3046875" customWidth="1"/>
     <col min="14" max="14" width="12.15234375" customWidth="1"/>
     <col min="15" max="15" width="12.23046875" customWidth="1"/>
-    <col min="16" max="16" width="17.07421875" customWidth="1"/>
-    <col min="17" max="17" width="11.4609375" customWidth="1"/>
-    <col min="16379" max="16379" width="11.4609375" customWidth="1"/>
-    <col min="16380" max="16384" width="11.53515625" customWidth="1"/>
+    <col min="16" max="18" width="17.07421875" customWidth="1"/>
+    <col min="19" max="19" width="23.84375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.61328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.84375" bestFit="1" customWidth="1"/>
+    <col min="16383" max="16383" width="11.4609375" customWidth="1"/>
+    <col min="16384" max="16384" width="11.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="37" customFormat="1" ht="25.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" s="37" customFormat="1" ht="25.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="57" t="s">
         <v>66</v>
       </c>
@@ -13671,8 +13769,20 @@
       <c r="Q1" s="59" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R1" s="59" t="s">
+        <v>697</v>
+      </c>
+      <c r="S1" s="59" t="s">
+        <v>698</v>
+      </c>
+      <c r="T1" s="59" t="s">
+        <v>699</v>
+      </c>
+      <c r="U1" s="59" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="55"/>
       <c r="B2" s="54"/>
       <c r="C2" s="55"/>
@@ -13690,8 +13800,12 @@
       <c r="O2" s="54"/>
       <c r="P2" s="54"/>
       <c r="Q2" s="54"/>
-    </row>
-    <row r="3" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+    </row>
+    <row r="3" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56"/>
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
@@ -13709,8 +13823,12 @@
       <c r="O3" s="56"/>
       <c r="P3" s="56"/>
       <c r="Q3" s="56"/>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56"/>
       <c r="B4" s="56"/>
       <c r="C4" s="56"/>
@@ -13728,8 +13846,12 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="56"/>
+    </row>
+    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56"/>
       <c r="B5" s="56"/>
       <c r="C5" s="56"/>
@@ -13747,8 +13869,12 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-    </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56"/>
       <c r="B6" s="56"/>
       <c r="C6" s="56"/>
@@ -13766,8 +13892,12 @@
       <c r="O6" s="56"/>
       <c r="P6" s="56"/>
       <c r="Q6" s="56"/>
-    </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R6" s="56"/>
+      <c r="S6" s="56"/>
+      <c r="T6" s="56"/>
+      <c r="U6" s="56"/>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56"/>
       <c r="B7" s="56"/>
       <c r="C7" s="56"/>
@@ -13785,8 +13915,12 @@
       <c r="O7" s="56"/>
       <c r="P7" s="56"/>
       <c r="Q7" s="56"/>
-    </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="56"/>
+      <c r="U7" s="56"/>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56"/>
       <c r="B8" s="56"/>
       <c r="C8" s="56"/>
@@ -13804,15 +13938,19 @@
       <c r="O8" s="56"/>
       <c r="P8" s="56"/>
       <c r="Q8" s="56"/>
-    </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+      <c r="R8" s="56"/>
+      <c r="S8" s="56"/>
+      <c r="T8" s="56"/>
+      <c r="U8" s="56"/>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>

--- a/Templates/MIAPPE_Spreadsheet_Template.xlsx
+++ b/Templates/MIAPPE_Spreadsheet_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\MIAPPE\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B29B008-B3ED-42A1-BE9D-B98EF601CD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8203694-3FCC-49FE-B693-04E767C996D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="891" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="891" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -2186,9 +2186,6 @@
   </si>
   <si>
     <t>S2</t>
-  </si>
-  <si>
-    <t>parentStudyId</t>
   </si>
   <si>
     <t>envParamAccession</t>
@@ -2343,6 +2340,9 @@
   <si>
     <t>S1-N-N1</t>
   </si>
+  <si>
+    <t>sourceStudyId</t>
+  </si>
 </sst>
 </file>
 
@@ -2351,7 +2351,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2543,6 +2543,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF247A00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2602,7 +2610,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2765,6 +2773,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5567,7 +5578,7 @@
   <autoFilter ref="A1:T3" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="96"/>
-    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="parentStudyId" dataDxfId="95"/>
+    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="sourceStudyId" dataDxfId="95"/>
     <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="94"/>
     <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="93"/>
     <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="92"/>
@@ -5952,7 +5963,7 @@
     </row>
     <row r="3" spans="1:20 16374:16384" s="9" customFormat="1" ht="98.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -10243,7 +10254,7 @@
         <v>299</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D1" s="52" t="s">
         <v>300</v>
@@ -10269,7 +10280,7 @@
       <c r="A2" s="30"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="30"/>
@@ -13754,7 +13765,7 @@
         <v>389</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E1" s="54" t="s">
         <v>391</v>
@@ -13763,22 +13774,22 @@
         <v>392</v>
       </c>
       <c r="G1" s="56" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1" s="56" t="s">
         <v>394</v>
       </c>
       <c r="I1" s="56" t="s">
+        <v>692</v>
+      </c>
+      <c r="J1" s="56" t="s">
         <v>693</v>
-      </c>
-      <c r="J1" s="56" t="s">
-        <v>694</v>
       </c>
       <c r="K1" s="54" t="s">
         <v>397</v>
       </c>
       <c r="L1" s="56" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="M1" s="55" t="s">
         <v>399</v>
@@ -13790,22 +13801,22 @@
         <v>401</v>
       </c>
       <c r="P1" s="56" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="Q1" s="56" t="s">
         <v>403</v>
       </c>
       <c r="R1" s="56" t="s">
+        <v>696</v>
+      </c>
+      <c r="S1" s="56" t="s">
         <v>697</v>
       </c>
-      <c r="S1" s="56" t="s">
+      <c r="T1" s="56" t="s">
         <v>698</v>
       </c>
-      <c r="T1" s="56" t="s">
+      <c r="U1" s="56" t="s">
         <v>699</v>
-      </c>
-      <c r="U1" s="56" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14989,29 +15000,29 @@
         <v>270</v>
       </c>
       <c r="B1" s="60" t="s">
+        <v>673</v>
+      </c>
+      <c r="C1" s="60" t="s">
         <v>674</v>
-      </c>
-      <c r="C1" s="60" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="61" t="s">
+        <v>675</v>
+      </c>
+      <c r="B2" s="62" t="s">
         <v>676</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="C2" t="s">
         <v>677</v>
-      </c>
-      <c r="C2" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>678</v>
+      </c>
+      <c r="B3" s="62" t="s">
         <v>679</v>
-      </c>
-      <c r="B3" s="62" t="s">
-        <v>680</v>
       </c>
     </row>
   </sheetData>
@@ -19568,8 +19579,8 @@
       <c r="A1" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="52" t="s">
-        <v>673</v>
+      <c r="B1" s="66" t="s">
+        <v>701</v>
       </c>
       <c r="C1" s="52" t="s">
         <v>67</v>
@@ -24327,10 +24338,10 @@
         <v>66</v>
       </c>
       <c r="B1" s="52" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C1" s="64" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D1" s="52" t="s">
         <v>282</v>
@@ -24356,7 +24367,7 @@
         <v>671</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C2" s="30" t="str">
         <f>CONCATENATE(experimentalFactor[studyId],"-",experimentalFactor[expeFactorCode])</f>
@@ -24559,31 +24570,31 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B1" s="65" t="s">
+        <v>684</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>689</v>
+      </c>
+      <c r="D1" t="s">
         <v>685</v>
       </c>
-      <c r="C1" s="60" t="s">
-        <v>690</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>686</v>
-      </c>
-      <c r="E1" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B2" t="str">
         <f>CONCATENATE(experimentalFactorLevel[expeFactorId],"-",experimentalFactorLevel[expeFactorLevelCode])</f>
         <v>S1-N-N1</v>
       </c>
       <c r="C2" s="60" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>

--- a/Templates/MIAPPE_Spreadsheet_Template.xlsx
+++ b/Templates/MIAPPE_Spreadsheet_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\MIAPPE\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8203694-3FCC-49FE-B693-04E767C996D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D6E3BB-274C-4AD8-8440-6EF7D8E42893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="891" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="891" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="703">
   <si>
     <t>README</t>
   </si>
@@ -2342,6 +2342,9 @@
   </si>
   <si>
     <t>sourceStudyId</t>
+  </si>
+  <si>
+    <t>sourceObsUnitId</t>
   </si>
 </sst>
 </file>
@@ -2781,7 +2784,27 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="139">
+  <dxfs count="140">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5460,15 +5483,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="MiappeStyle" pivot="0" count="9" xr9:uid="{59C54380-D204-4007-9CC6-0890CCDEE3C9}">
-      <tableStyleElement type="wholeTable" dxfId="138"/>
-      <tableStyleElement type="headerRow" dxfId="137"/>
-      <tableStyleElement type="totalRow" dxfId="136"/>
-      <tableStyleElement type="firstColumn" dxfId="135"/>
-      <tableStyleElement type="lastColumn" dxfId="134"/>
-      <tableStyleElement type="firstRowStripe" dxfId="133"/>
-      <tableStyleElement type="secondRowStripe" dxfId="132"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="131"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="130"/>
+      <tableStyleElement type="wholeTable" dxfId="139"/>
+      <tableStyleElement type="headerRow" dxfId="138"/>
+      <tableStyleElement type="totalRow" dxfId="137"/>
+      <tableStyleElement type="firstColumn" dxfId="136"/>
+      <tableStyleElement type="lastColumn" dxfId="135"/>
+      <tableStyleElement type="firstRowStripe" dxfId="134"/>
+      <tableStyleElement type="secondRowStripe" dxfId="133"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="132"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="131"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5483,86 +5506,87 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}" name="investigation" displayName="investigation" ref="A1:H2" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}" name="investigation" displayName="investigation" ref="A1:H2" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107">
   <autoFilter ref="A1:H2" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{25F01F79-3E24-44AF-B5E3-4EB20FD9A360}" name="investigationId" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{16E59F0F-AC6D-4504-A428-E7D7AC601401}" name="investigationTitle" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{4668A34F-CEFF-43A7-84AA-B014E3A90F47}" name="investigationDescription" dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{403353FA-EBA5-418F-8273-81472CDF29D4}" name="submissionDate" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{18E43DB3-511F-4E0E-B357-B4A6E40F0660}" name="publicReleaseDate" dataDxfId="101"/>
-    <tableColumn id="6" xr3:uid="{91C01C8C-69AF-4B74-BA16-1C962EDAF32D}" name="license" dataDxfId="100"/>
-    <tableColumn id="7" xr3:uid="{E94BB99A-781A-4442-AD9C-7E4D99028DC9}" name="miappeVersion" dataDxfId="99"/>
-    <tableColumn id="8" xr3:uid="{91B9E445-65BD-412A-95C1-EA371F946FCA}" name="associatedPublication" dataDxfId="98"/>
+    <tableColumn id="1" xr3:uid="{25F01F79-3E24-44AF-B5E3-4EB20FD9A360}" name="investigationId" dataDxfId="106"/>
+    <tableColumn id="2" xr3:uid="{16E59F0F-AC6D-4504-A428-E7D7AC601401}" name="investigationTitle" dataDxfId="105"/>
+    <tableColumn id="3" xr3:uid="{4668A34F-CEFF-43A7-84AA-B014E3A90F47}" name="investigationDescription" dataDxfId="104"/>
+    <tableColumn id="4" xr3:uid="{403353FA-EBA5-418F-8273-81472CDF29D4}" name="submissionDate" dataDxfId="103"/>
+    <tableColumn id="5" xr3:uid="{18E43DB3-511F-4E0E-B357-B4A6E40F0660}" name="publicReleaseDate" dataDxfId="102"/>
+    <tableColumn id="6" xr3:uid="{91C01C8C-69AF-4B74-BA16-1C962EDAF32D}" name="license" dataDxfId="101"/>
+    <tableColumn id="7" xr3:uid="{E94BB99A-781A-4442-AD9C-7E4D99028DC9}" name="miappeVersion" dataDxfId="100"/>
+    <tableColumn id="8" xr3:uid="{91B9E445-65BD-412A-95C1-EA371F946FCA}" name="associatedPublication" dataDxfId="99"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:G2" insertRow="1" totalsRowShown="0" dataDxfId="18">
-  <autoFilter ref="A1:G2" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:H2" insertRow="1" totalsRowShown="0" dataDxfId="19">
+  <autoFilter ref="A1:H2" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{F4D9572F-C227-480C-812D-9943C387240C}" name="sourceObsUnitId" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:G2" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{92A1E618-2F85-46E4-B7EF-76ED045C215B}" name="obsUnitId" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{A0DFEC37-340B-4DF8-907B-A9769602FD28}" name="sampleId" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{D455AF29-BE41-4DDA-A9B2-A46F4EEA6767}" name="developmentStage" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{C24109D3-E8A6-4810-A0A6-ACD6730F0D08}" name="anatomicalEntity" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{5C630D57-B424-4325-BC0C-BEEBEDC89DBB}" name="sampleDesc" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{CDEC6C64-2387-4FCF-9A2C-63F54020D0A0}" name="collectionDate" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{FFB2A4F7-3C7D-4BC5-AD9E-C14C20349305}" name="externalId" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{92A1E618-2F85-46E4-B7EF-76ED045C215B}" name="obsUnitId" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{A0DFEC37-340B-4DF8-907B-A9769602FD28}" name="sampleId" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{D455AF29-BE41-4DDA-A9B2-A46F4EEA6767}" name="developmentStage" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{C24109D3-E8A6-4810-A0A6-ACD6730F0D08}" name="anatomicalEntity" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{5C630D57-B424-4325-BC0C-BEEBEDC89DBB}" name="sampleDesc" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{CDEC6C64-2387-4FCF-9A2C-63F54020D0A0}" name="collectionDate" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{FFB2A4F7-3C7D-4BC5-AD9E-C14C20349305}" name="externalId" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:U2" insertRow="1" totalsRowShown="0" dataDxfId="129">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:U2" insertRow="1" totalsRowShown="0" dataDxfId="130">
   <autoFilter ref="A1:U2" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="128"/>
-    <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccession" dataDxfId="125"/>
-    <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="124"/>
-    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="123"/>
-    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccession" dataDxfId="122"/>
-    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="121"/>
-    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccession" dataDxfId="120"/>
-    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccession" dataDxfId="119"/>
-    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="118"/>
-    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccession" dataDxfId="117"/>
-    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="116"/>
-    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="115"/>
-    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="114"/>
-    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccession" dataDxfId="113"/>
-    <tableColumn id="19" xr3:uid="{EE91A801-8376-4314-ADFB-6E32C3AE8AE4}" name="timeScale" dataDxfId="112"/>
-    <tableColumn id="22" xr3:uid="{A52D8785-E3B2-4548-AA8A-0964285F0DB9}" name="participant" dataDxfId="111"/>
-    <tableColumn id="21" xr3:uid="{CA21FA4C-5A61-4852-9BA7-6FDDF22D4ADC}" name="participantAccession" dataDxfId="110"/>
-    <tableColumn id="20" xr3:uid="{3DF54E16-A553-4C7E-9762-C6517F5AD994}" name="participantRole" dataDxfId="109"/>
-    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="participantRoleAccession" dataDxfId="108"/>
+    <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="129"/>
+    <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="128"/>
+    <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="127"/>
+    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccession" dataDxfId="126"/>
+    <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="124"/>
+    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccession" dataDxfId="123"/>
+    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccession" dataDxfId="121"/>
+    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccession" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccession" dataDxfId="118"/>
+    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="117"/>
+    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="116"/>
+    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="115"/>
+    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccession" dataDxfId="114"/>
+    <tableColumn id="19" xr3:uid="{EE91A801-8376-4314-ADFB-6E32C3AE8AE4}" name="timeScale" dataDxfId="113"/>
+    <tableColumn id="22" xr3:uid="{A52D8785-E3B2-4548-AA8A-0964285F0DB9}" name="participant" dataDxfId="112"/>
+    <tableColumn id="21" xr3:uid="{CA21FA4C-5A61-4852-9BA7-6FDDF22D4ADC}" name="participantAccession" dataDxfId="111"/>
+    <tableColumn id="20" xr3:uid="{3DF54E16-A553-4C7E-9762-C6517F5AD994}" name="participantRole" dataDxfId="110"/>
+    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="participantRoleAccession" dataDxfId="109"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}" name="environmentParameters" displayName="environmentParameters" ref="A1:C3" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}" name="environmentParameters" displayName="environmentParameters" ref="A1:C3" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:C3" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{5E761B2A-3F92-4181-AF5D-F423F0564A09}" name="envParam"/>
@@ -5574,119 +5598,119 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:T3" totalsRowShown="0" dataDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:T3" totalsRowShown="0" dataDxfId="98">
   <autoFilter ref="A1:T3" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="96"/>
-    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="sourceStudyId" dataDxfId="95"/>
-    <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="94"/>
-    <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="93"/>
-    <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="92"/>
-    <tableColumn id="5" xr3:uid="{E557DB42-3379-4598-AAF9-21798BC64DAB}" name="studyEndDate" dataDxfId="91"/>
-    <tableColumn id="6" xr3:uid="{1EEA2EC5-CA19-40B4-9DFB-2DE9A9E916EA}" name="contactInst" dataDxfId="90"/>
-    <tableColumn id="7" xr3:uid="{E0A5C222-CFE5-4E9C-8E84-0892043DBD21}" name="locationCountry" dataDxfId="89"/>
-    <tableColumn id="8" xr3:uid="{7B635D2A-56C5-48B0-A880-E33ADE030AB1}" name="siteName" dataDxfId="88"/>
-    <tableColumn id="9" xr3:uid="{2F8227C3-F11C-4DAA-93EB-CEBD94FF81A9}" name="locationLatitude" dataDxfId="87"/>
-    <tableColumn id="10" xr3:uid="{6A14EB46-0BF4-45C6-9048-E1B7D13E633A}" name="locationLongitude" dataDxfId="86"/>
-    <tableColumn id="11" xr3:uid="{9954429A-AA41-408C-BB04-D73EDB89D73F}" name="locationAltitude" dataDxfId="85"/>
-    <tableColumn id="12" xr3:uid="{39FEDA43-D994-4742-B319-3DFED43EF79B}" name="expeDesignDesc" dataDxfId="84"/>
-    <tableColumn id="13" xr3:uid="{C9F6A881-1CF1-4AD9-8305-B7E26FD78E3B}" name="expeDesignType" dataDxfId="83"/>
-    <tableColumn id="14" xr3:uid="{253A58C7-1A2A-4D25-9622-3AE33F89A685}" name="obsUnitLevelHierarchy" dataDxfId="82"/>
-    <tableColumn id="15" xr3:uid="{10DCEB5F-0BF5-4476-83E5-B973A516A8CD}" name="obsUnitDesc" dataDxfId="81"/>
-    <tableColumn id="16" xr3:uid="{0D36E7FE-2245-4B79-9A59-4C64590731A5}" name="growthFacilityDesc" dataDxfId="80"/>
-    <tableColumn id="17" xr3:uid="{599307E8-6E88-4D3F-BF48-ADF70D109D18}" name="growthFacilityType" dataDxfId="79"/>
-    <tableColumn id="18" xr3:uid="{63403E81-283C-4E2E-984D-9EFC0886E90C}" name="culturalPractice" dataDxfId="78"/>
-    <tableColumn id="19" xr3:uid="{E74D4B3A-67BC-482F-8485-FC7D9088A8B6}" name="expeDesignMap" dataDxfId="77"/>
+    <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="97"/>
+    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="sourceStudyId" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="94"/>
+    <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{E557DB42-3379-4598-AAF9-21798BC64DAB}" name="studyEndDate" dataDxfId="92"/>
+    <tableColumn id="6" xr3:uid="{1EEA2EC5-CA19-40B4-9DFB-2DE9A9E916EA}" name="contactInst" dataDxfId="91"/>
+    <tableColumn id="7" xr3:uid="{E0A5C222-CFE5-4E9C-8E84-0892043DBD21}" name="locationCountry" dataDxfId="90"/>
+    <tableColumn id="8" xr3:uid="{7B635D2A-56C5-48B0-A880-E33ADE030AB1}" name="siteName" dataDxfId="89"/>
+    <tableColumn id="9" xr3:uid="{2F8227C3-F11C-4DAA-93EB-CEBD94FF81A9}" name="locationLatitude" dataDxfId="88"/>
+    <tableColumn id="10" xr3:uid="{6A14EB46-0BF4-45C6-9048-E1B7D13E633A}" name="locationLongitude" dataDxfId="87"/>
+    <tableColumn id="11" xr3:uid="{9954429A-AA41-408C-BB04-D73EDB89D73F}" name="locationAltitude" dataDxfId="86"/>
+    <tableColumn id="12" xr3:uid="{39FEDA43-D994-4742-B319-3DFED43EF79B}" name="expeDesignDesc" dataDxfId="85"/>
+    <tableColumn id="13" xr3:uid="{C9F6A881-1CF1-4AD9-8305-B7E26FD78E3B}" name="expeDesignType" dataDxfId="84"/>
+    <tableColumn id="14" xr3:uid="{253A58C7-1A2A-4D25-9622-3AE33F89A685}" name="obsUnitLevelHierarchy" dataDxfId="83"/>
+    <tableColumn id="15" xr3:uid="{10DCEB5F-0BF5-4476-83E5-B973A516A8CD}" name="obsUnitDesc" dataDxfId="82"/>
+    <tableColumn id="16" xr3:uid="{0D36E7FE-2245-4B79-9A59-4C64590731A5}" name="growthFacilityDesc" dataDxfId="81"/>
+    <tableColumn id="17" xr3:uid="{599307E8-6E88-4D3F-BF48-ADF70D109D18}" name="growthFacilityType" dataDxfId="80"/>
+    <tableColumn id="18" xr3:uid="{63403E81-283C-4E2E-984D-9EFC0886E90C}" name="culturalPractice" dataDxfId="79"/>
+    <tableColumn id="19" xr3:uid="{E74D4B3A-67BC-482F-8485-FC7D9088A8B6}" name="expeDesignMap" dataDxfId="78"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}" name="person" displayName="person" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}" name="person" displayName="person" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="77" dataDxfId="76">
   <autoFilter ref="A1:F2" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{49A703DB-336A-4F60-9DA6-8249763A2765}" name="studyId" dataDxfId="74"/>
-    <tableColumn id="2" xr3:uid="{65039BF4-A122-4B88-8EB2-FD3ED61B8912}" name="personName" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{4B7588A4-B756-4E28-B8A4-AFB8D62031B4}" name="personEmail" dataDxfId="72"/>
-    <tableColumn id="4" xr3:uid="{639FC837-B543-4A62-B2C2-3EE761EF5EF7}" name="personId" dataDxfId="71"/>
-    <tableColumn id="5" xr3:uid="{593F31A8-CDAA-47CF-89F3-2902C6B8D3C8}" name="personRole" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{5FCF059F-31D5-4218-8D81-DC379C42EAF4}" name="personAffiliation" dataDxfId="69"/>
+    <tableColumn id="1" xr3:uid="{49A703DB-336A-4F60-9DA6-8249763A2765}" name="studyId" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{65039BF4-A122-4B88-8EB2-FD3ED61B8912}" name="personName" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{4B7588A4-B756-4E28-B8A4-AFB8D62031B4}" name="personEmail" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{639FC837-B543-4A62-B2C2-3EE761EF5EF7}" name="personId" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{593F31A8-CDAA-47CF-89F3-2902C6B8D3C8}" name="personRole" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{5FCF059F-31D5-4218-8D81-DC379C42EAF4}" name="personAffiliation" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}" name="dataFile" displayName="dataFile" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}" name="dataFile" displayName="dataFile" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="A1:D2" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AD6A7B95-2E4C-4264-86B4-35031C8932E3}" name="studyId" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{A5C92CF7-B78F-4910-A250-8A16D6E7889C}" name="dataFileLink" dataDxfId="65"/>
-    <tableColumn id="3" xr3:uid="{620AC217-74DA-496A-9696-16EF7D98E86C}" name="dataFileDesc" dataDxfId="64"/>
-    <tableColumn id="4" xr3:uid="{79F128D7-FDA0-4F62-B04B-DAEE7E495850}" name="dataFileVersion" dataDxfId="63"/>
+    <tableColumn id="1" xr3:uid="{AD6A7B95-2E4C-4264-86B4-35031C8932E3}" name="studyId" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{A5C92CF7-B78F-4910-A250-8A16D6E7889C}" name="dataFileLink" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{620AC217-74DA-496A-9696-16EF7D98E86C}" name="dataFileDesc" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{79F128D7-FDA0-4F62-B04B-DAEE7E495850}" name="dataFileVersion" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}" name="biologicalMaterial" displayName="biologicalMaterial" ref="A1:X2" insertRow="1" totalsRowShown="0" headerRowDxfId="62" dataDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}" name="biologicalMaterial" displayName="biologicalMaterial" ref="A1:X2" insertRow="1" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:X2" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}"/>
   <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{71E6992E-3AF7-4C8A-9C1E-930C105005E2}" name="studyId" dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{BA8B45A2-9F79-4EE6-A38F-EF56D5CE4A1A}" name="biologicalMaterialId" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{546FEA19-FA9D-47D3-BF6E-57CDA029B0A3}" name="biologicalMaterialExtId" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{0DD21880-A5E2-4076-AA9F-554DE7C7E0D1}" name="organism" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{9760C8F1-7162-4A84-80C2-FBEC779AFAD0}" name="genus" dataDxfId="56"/>
-    <tableColumn id="6" xr3:uid="{D7026284-DE40-4B04-A583-983A0B5FB5BB}" name="species" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{22046373-BBD5-4919-AC4C-AA8E91D97026}" name="infraspecificName" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{579B0DCA-BD9C-4E7B-BB3B-3FB19A4CBCA3}" name="biologicalMaterialLatitude" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{A7E064AC-CDCF-4898-BEF3-07CF88887A4E}" name="biologicalMaterialLongitude" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{D55DD07C-0BE6-4D7D-80E1-B7195245711A}" name="biologicalMaterialAltitude" dataDxfId="51"/>
-    <tableColumn id="11" xr3:uid="{CA82A017-8E46-417C-9A1F-D7010C7B489F}" name="biologicalMaterialCoordUncertainty" dataDxfId="50"/>
-    <tableColumn id="12" xr3:uid="{16F6B082-1241-4094-AFDC-6E6F5B63F502}" name="biologicalMaterialPreprocessing" dataDxfId="49"/>
-    <tableColumn id="13" xr3:uid="{16F5564F-9F1B-4CEB-8DEC-4F46E89C2EB5}" name="materialSourceId" dataDxfId="48"/>
-    <tableColumn id="14" xr3:uid="{0AB5DA63-1709-41B8-9FAD-5B1A8A45E649}" name="materialSourceDoi" dataDxfId="47"/>
-    <tableColumn id="15" xr3:uid="{26116E4A-CA0A-4D6C-A863-AEA24B0E0C24}" name="materialSourceAccNumber" dataDxfId="46"/>
-    <tableColumn id="16" xr3:uid="{0C2E647E-5127-470F-859E-ED727EEFA3B9}" name="materialSourceAccName" dataDxfId="45"/>
-    <tableColumn id="17" xr3:uid="{B6097563-29EF-4C10-9096-04A2C164B15A}" name="materialSourceInstCode" dataDxfId="44"/>
-    <tableColumn id="18" xr3:uid="{BEA38246-EAA3-4450-B29F-D608607C2513}" name="materialSourceInstName" dataDxfId="43"/>
-    <tableColumn id="19" xr3:uid="{E8257013-CD5D-4534-9CD0-08D9EBBE7EF0}" name="materialSourceOtherIds" dataDxfId="42"/>
-    <tableColumn id="20" xr3:uid="{BE0E6D94-2ED0-4863-9DE5-9AA6BD4643D6}" name="materialSourceLatitude" dataDxfId="41"/>
-    <tableColumn id="21" xr3:uid="{BD849876-C99C-4475-87D4-DEECBE575F67}" name="materialSourceLongitude" dataDxfId="40"/>
-    <tableColumn id="22" xr3:uid="{0C871681-B897-43DD-A6BE-F03CAA6574F6}" name="materialSourceAltitude" dataDxfId="39"/>
-    <tableColumn id="23" xr3:uid="{ECC67BD8-3E1F-4A97-95B0-A9CCE07839CA}" name="materialSourceCoordUncertainty" dataDxfId="38"/>
-    <tableColumn id="24" xr3:uid="{C66E78D2-DB97-4D59-8D52-ECE79ED6BB86}" name="materialSourceDesc" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{71E6992E-3AF7-4C8A-9C1E-930C105005E2}" name="studyId" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{BA8B45A2-9F79-4EE6-A38F-EF56D5CE4A1A}" name="biologicalMaterialId" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{546FEA19-FA9D-47D3-BF6E-57CDA029B0A3}" name="biologicalMaterialExtId" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{0DD21880-A5E2-4076-AA9F-554DE7C7E0D1}" name="organism" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{9760C8F1-7162-4A84-80C2-FBEC779AFAD0}" name="genus" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{D7026284-DE40-4B04-A583-983A0B5FB5BB}" name="species" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{22046373-BBD5-4919-AC4C-AA8E91D97026}" name="infraspecificName" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{579B0DCA-BD9C-4E7B-BB3B-3FB19A4CBCA3}" name="biologicalMaterialLatitude" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{A7E064AC-CDCF-4898-BEF3-07CF88887A4E}" name="biologicalMaterialLongitude" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{D55DD07C-0BE6-4D7D-80E1-B7195245711A}" name="biologicalMaterialAltitude" dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{CA82A017-8E46-417C-9A1F-D7010C7B489F}" name="biologicalMaterialCoordUncertainty" dataDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{16F6B082-1241-4094-AFDC-6E6F5B63F502}" name="biologicalMaterialPreprocessing" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{16F5564F-9F1B-4CEB-8DEC-4F46E89C2EB5}" name="materialSourceId" dataDxfId="49"/>
+    <tableColumn id="14" xr3:uid="{0AB5DA63-1709-41B8-9FAD-5B1A8A45E649}" name="materialSourceDoi" dataDxfId="48"/>
+    <tableColumn id="15" xr3:uid="{26116E4A-CA0A-4D6C-A863-AEA24B0E0C24}" name="materialSourceAccNumber" dataDxfId="47"/>
+    <tableColumn id="16" xr3:uid="{0C2E647E-5127-470F-859E-ED727EEFA3B9}" name="materialSourceAccName" dataDxfId="46"/>
+    <tableColumn id="17" xr3:uid="{B6097563-29EF-4C10-9096-04A2C164B15A}" name="materialSourceInstCode" dataDxfId="45"/>
+    <tableColumn id="18" xr3:uid="{BEA38246-EAA3-4450-B29F-D608607C2513}" name="materialSourceInstName" dataDxfId="44"/>
+    <tableColumn id="19" xr3:uid="{E8257013-CD5D-4534-9CD0-08D9EBBE7EF0}" name="materialSourceOtherIds" dataDxfId="43"/>
+    <tableColumn id="20" xr3:uid="{BE0E6D94-2ED0-4863-9DE5-9AA6BD4643D6}" name="materialSourceLatitude" dataDxfId="42"/>
+    <tableColumn id="21" xr3:uid="{BD849876-C99C-4475-87D4-DEECBE575F67}" name="materialSourceLongitude" dataDxfId="41"/>
+    <tableColumn id="22" xr3:uid="{0C871681-B897-43DD-A6BE-F03CAA6574F6}" name="materialSourceAltitude" dataDxfId="40"/>
+    <tableColumn id="23" xr3:uid="{ECC67BD8-3E1F-4A97-95B0-A9CCE07839CA}" name="materialSourceCoordUncertainty" dataDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{C66E78D2-DB97-4D59-8D52-ECE79ED6BB86}" name="materialSourceDesc" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}" name="environment" displayName="environment" ref="A1:C2" insertRow="1" totalsRowShown="0" headerRowDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}" name="environment" displayName="environment" ref="A1:C2" insertRow="1" totalsRowShown="0" headerRowDxfId="37">
   <autoFilter ref="A1:C2" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{08C0BD82-D970-44E6-99E3-B4872FECEFE5}" name="studyId" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{F9DC7CC5-88B3-4A9A-B462-9FB971836B81}" name="envParam" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{65E72A00-3C03-4A17-922C-EE6A4A3D8D80}" name="envParamValue" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{08C0BD82-D970-44E6-99E3-B4872FECEFE5}" name="studyId" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{F9DC7CC5-88B3-4A9A-B462-9FB971836B81}" name="envParam" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{65E72A00-3C03-4A17-922C-EE6A4A3D8D80}" name="envParamValue" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}" name="experimentalFactor" displayName="experimentalFactor" ref="A1:F2" totalsRowShown="0" headerRowDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}" name="experimentalFactor" displayName="experimentalFactor" ref="A1:F2" totalsRowShown="0" headerRowDxfId="33">
   <autoFilter ref="A1:F2" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{8AF0BF35-BAC4-4E9A-A1CC-B83DC7399496}" name="expeFactorCode" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{67BFB12E-F4AF-4C45-B7B6-4791A656C30A}" name="expeFactorId" dataDxfId="29">
+    <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{8AF0BF35-BAC4-4E9A-A1CC-B83DC7399496}" name="expeFactorCode" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{67BFB12E-F4AF-4C45-B7B6-4791A656C30A}" name="expeFactorId" dataDxfId="30">
       <calculatedColumnFormula>CONCATENATE(experimentalFactor[studyId],"-",experimentalFactor[expeFactorCode])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5709,16 +5733,16 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:G2" totalsRowShown="0" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:G2" totalsRowShown="0" dataDxfId="26">
   <autoFilter ref="A1:G2" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{DB25986C-BD6F-40F9-A226-C9A11BBDF460}" name="studyId" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{6EE72788-DEAD-4FC0-9383-C6415EC5E8A5}" name="obsUnitId" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{59210F7A-BDE1-4221-BA01-D09327E85900}" name="expeFactorLevelId" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{0DDCD5FF-AC45-4794-9B28-BBD982C1FB84}" name="eventType" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{DB25986C-BD6F-40F9-A226-C9A11BBDF460}" name="studyId" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{6EE72788-DEAD-4FC0-9383-C6415EC5E8A5}" name="obsUnitId" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{59210F7A-BDE1-4221-BA01-D09327E85900}" name="expeFactorLevelId" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{0DDCD5FF-AC45-4794-9B28-BBD982C1FB84}" name="eventType" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11409,15 +11433,14 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:M997"/>
+  <dimension ref="A1:N997"/>
   <sheetFormatPr defaultColWidth="14.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="20.42578125" customWidth="1"/>
-    <col min="8" max="13" width="10.5703125" customWidth="1"/>
-    <col min="16384" max="16384" width="11.42578125" customWidth="1"/>
+    <col min="1" max="8" width="20.42578125" customWidth="1"/>
+    <col min="9" max="14" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="36" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="36" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
         <v>66</v>
       </c>
@@ -11427,41 +11450,45 @@
       <c r="C1" s="52" t="s">
         <v>299</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="66" t="s">
+        <v>702</v>
+      </c>
+      <c r="E1" s="52" t="s">
         <v>323</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="F1" s="53" t="s">
         <v>324</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="G1" s="51" t="s">
         <v>325</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="H1" s="51" t="s">
         <v>326</v>
       </c>
-      <c r="H1" s="41"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="41"/>
       <c r="L1" s="41"/>
       <c r="M1" s="41"/>
-    </row>
-    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N1" s="41"/>
+    </row>
+    <row r="2" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="30"/>
       <c r="F2" s="13"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="43"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="30"/>
       <c r="I2" s="43"/>
       <c r="J2" s="43"/>
       <c r="K2" s="43"/>
       <c r="L2" s="43"/>
       <c r="M2" s="43"/>
-    </row>
-    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N2" s="43"/>
+    </row>
+    <row r="3" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -11469,14 +11496,15 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="43"/>
+      <c r="H3" s="7"/>
       <c r="I3" s="43"/>
       <c r="J3" s="43"/>
       <c r="K3" s="43"/>
       <c r="L3" s="43"/>
       <c r="M3" s="43"/>
-    </row>
-    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N3" s="43"/>
+    </row>
+    <row r="4" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -11484,14 +11512,15 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="43"/>
+      <c r="H4" s="7"/>
       <c r="I4" s="43"/>
       <c r="J4" s="43"/>
       <c r="K4" s="43"/>
       <c r="L4" s="43"/>
       <c r="M4" s="43"/>
-    </row>
-    <row r="5" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N4" s="43"/>
+    </row>
+    <row r="5" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -11499,14 +11528,15 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="43"/>
+      <c r="H5" s="7"/>
       <c r="I5" s="43"/>
       <c r="J5" s="43"/>
       <c r="K5" s="43"/>
       <c r="L5" s="43"/>
       <c r="M5" s="43"/>
-    </row>
-    <row r="6" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N5" s="43"/>
+    </row>
+    <row r="6" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -11514,14 +11544,15 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="43"/>
+      <c r="H6" s="7"/>
       <c r="I6" s="43"/>
       <c r="J6" s="43"/>
       <c r="K6" s="43"/>
       <c r="L6" s="43"/>
       <c r="M6" s="43"/>
-    </row>
-    <row r="7" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N6" s="43"/>
+    </row>
+    <row r="7" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -11529,14 +11560,15 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="43"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="43"/>
       <c r="J7" s="43"/>
       <c r="K7" s="43"/>
       <c r="L7" s="43"/>
       <c r="M7" s="43"/>
-    </row>
-    <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N7" s="43"/>
+    </row>
+    <row r="8" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -11544,14 +11576,15 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="43"/>
+      <c r="H8" s="7"/>
       <c r="I8" s="43"/>
       <c r="J8" s="43"/>
       <c r="K8" s="43"/>
       <c r="L8" s="43"/>
       <c r="M8" s="43"/>
-    </row>
-    <row r="9" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N8" s="43"/>
+    </row>
+    <row r="9" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="43"/>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
@@ -11565,14 +11598,15 @@
       <c r="K9" s="43"/>
       <c r="L9" s="43"/>
       <c r="M9" s="43"/>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="N9" s="43"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12555,9 +12589,12 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{C9CAF3F9-1E81-44B5-A4D0-E0C67AD055FB}">
       <formula1>INDIRECT("study[studyId]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{65F4BB92-CA74-4B3B-B3E4-AF805E1DE54A}">
+      <formula1>INDIRECT("observationUnit[obsUnitId]")</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Templates/MIAPPE_Spreadsheet_Template.xlsx
+++ b/Templates/MIAPPE_Spreadsheet_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\MIAPPE\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D6E3BB-274C-4AD8-8440-6EF7D8E42893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708EF98F-A854-4F9C-BCC9-F878A55FB8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="891" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="891" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="704">
   <si>
     <t>README</t>
   </si>
@@ -2345,6 +2345,9 @@
   </si>
   <si>
     <t>sourceObsUnitId</t>
+  </si>
+  <si>
+    <t>dataFileType</t>
   </si>
 </sst>
 </file>
@@ -2784,7 +2787,27 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="140">
+  <dxfs count="141">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5483,15 +5506,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="MiappeStyle" pivot="0" count="9" xr9:uid="{59C54380-D204-4007-9CC6-0890CCDEE3C9}">
-      <tableStyleElement type="wholeTable" dxfId="139"/>
-      <tableStyleElement type="headerRow" dxfId="138"/>
-      <tableStyleElement type="totalRow" dxfId="137"/>
-      <tableStyleElement type="firstColumn" dxfId="136"/>
-      <tableStyleElement type="lastColumn" dxfId="135"/>
-      <tableStyleElement type="firstRowStripe" dxfId="134"/>
-      <tableStyleElement type="secondRowStripe" dxfId="133"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="132"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="131"/>
+      <tableStyleElement type="wholeTable" dxfId="140"/>
+      <tableStyleElement type="headerRow" dxfId="139"/>
+      <tableStyleElement type="totalRow" dxfId="138"/>
+      <tableStyleElement type="firstColumn" dxfId="137"/>
+      <tableStyleElement type="lastColumn" dxfId="136"/>
+      <tableStyleElement type="firstRowStripe" dxfId="135"/>
+      <tableStyleElement type="secondRowStripe" dxfId="134"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="133"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="132"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5506,87 +5529,87 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}" name="investigation" displayName="investigation" ref="A1:H2" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}" name="investigation" displayName="investigation" ref="A1:H2" totalsRowShown="0" headerRowDxfId="109" dataDxfId="108">
   <autoFilter ref="A1:H2" xr:uid="{D8AF6C71-E30B-48EC-A84C-21302F8FBBD8}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{25F01F79-3E24-44AF-B5E3-4EB20FD9A360}" name="investigationId" dataDxfId="106"/>
-    <tableColumn id="2" xr3:uid="{16E59F0F-AC6D-4504-A428-E7D7AC601401}" name="investigationTitle" dataDxfId="105"/>
-    <tableColumn id="3" xr3:uid="{4668A34F-CEFF-43A7-84AA-B014E3A90F47}" name="investigationDescription" dataDxfId="104"/>
-    <tableColumn id="4" xr3:uid="{403353FA-EBA5-418F-8273-81472CDF29D4}" name="submissionDate" dataDxfId="103"/>
-    <tableColumn id="5" xr3:uid="{18E43DB3-511F-4E0E-B357-B4A6E40F0660}" name="publicReleaseDate" dataDxfId="102"/>
-    <tableColumn id="6" xr3:uid="{91C01C8C-69AF-4B74-BA16-1C962EDAF32D}" name="license" dataDxfId="101"/>
-    <tableColumn id="7" xr3:uid="{E94BB99A-781A-4442-AD9C-7E4D99028DC9}" name="miappeVersion" dataDxfId="100"/>
-    <tableColumn id="8" xr3:uid="{91B9E445-65BD-412A-95C1-EA371F946FCA}" name="associatedPublication" dataDxfId="99"/>
+    <tableColumn id="1" xr3:uid="{25F01F79-3E24-44AF-B5E3-4EB20FD9A360}" name="investigationId" dataDxfId="107"/>
+    <tableColumn id="2" xr3:uid="{16E59F0F-AC6D-4504-A428-E7D7AC601401}" name="investigationTitle" dataDxfId="106"/>
+    <tableColumn id="3" xr3:uid="{4668A34F-CEFF-43A7-84AA-B014E3A90F47}" name="investigationDescription" dataDxfId="105"/>
+    <tableColumn id="4" xr3:uid="{403353FA-EBA5-418F-8273-81472CDF29D4}" name="submissionDate" dataDxfId="104"/>
+    <tableColumn id="5" xr3:uid="{18E43DB3-511F-4E0E-B357-B4A6E40F0660}" name="publicReleaseDate" dataDxfId="103"/>
+    <tableColumn id="6" xr3:uid="{91C01C8C-69AF-4B74-BA16-1C962EDAF32D}" name="license" dataDxfId="102"/>
+    <tableColumn id="7" xr3:uid="{E94BB99A-781A-4442-AD9C-7E4D99028DC9}" name="miappeVersion" dataDxfId="101"/>
+    <tableColumn id="8" xr3:uid="{91B9E445-65BD-412A-95C1-EA371F946FCA}" name="associatedPublication" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:H2" insertRow="1" totalsRowShown="0" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}" name="observationUnit" displayName="observationUnit" ref="A1:H2" insertRow="1" totalsRowShown="0" dataDxfId="20">
   <autoFilter ref="A1:H2" xr:uid="{9A4F6851-A82A-4719-850B-9015CB0F68F5}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{F4D9572F-C227-480C-812D-9943C387240C}" name="sourceObsUnitId" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{67885524-1B5C-4054-BDDA-7439D87C65A3}" name="studyId" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{BD42E68A-B0EE-4F6E-9323-7BF9B4395F28}" name="biologicalMaterialId" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{ADEBC7D5-74AA-4299-BAA7-2B546D4FD4E2}" name="obsUnitId" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{F4D9572F-C227-480C-812D-9943C387240C}" name="sourceObsUnitId" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{9981E5B4-9802-41A5-B134-7A7924A4B125}" name="obsUnitType" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{CB30098B-ECC6-437C-9C2E-46BB51031C94}" name="externalId" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{B9F1BB11-5258-49AF-A8C5-372071AA9FF3}" name="spatialDistribution" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{7E1C2129-988B-4857-85FE-0F1EA951EBC7}" name="obsUnitFactorValue" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}" name="sample" displayName="sample" ref="A1:G2" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:G2" xr:uid="{6D61A835-4FD1-495E-A537-D0167D8A5442}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{92A1E618-2F85-46E4-B7EF-76ED045C215B}" name="obsUnitId" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{A0DFEC37-340B-4DF8-907B-A9769602FD28}" name="sampleId" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{D455AF29-BE41-4DDA-A9B2-A46F4EEA6767}" name="developmentStage" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{C24109D3-E8A6-4810-A0A6-ACD6730F0D08}" name="anatomicalEntity" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{5C630D57-B424-4325-BC0C-BEEBEDC89DBB}" name="sampleDesc" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{CDEC6C64-2387-4FCF-9A2C-63F54020D0A0}" name="collectionDate" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{FFB2A4F7-3C7D-4BC5-AD9E-C14C20349305}" name="externalId" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{92A1E618-2F85-46E4-B7EF-76ED045C215B}" name="obsUnitId" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{A0DFEC37-340B-4DF8-907B-A9769602FD28}" name="sampleId" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{D455AF29-BE41-4DDA-A9B2-A46F4EEA6767}" name="developmentStage" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{C24109D3-E8A6-4810-A0A6-ACD6730F0D08}" name="anatomicalEntity" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{5C630D57-B424-4325-BC0C-BEEBEDC89DBB}" name="sampleDesc" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{CDEC6C64-2387-4FCF-9A2C-63F54020D0A0}" name="collectionDate" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{FFB2A4F7-3C7D-4BC5-AD9E-C14C20349305}" name="externalId" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:U2" insertRow="1" totalsRowShown="0" dataDxfId="130">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}" name="observedVariable" displayName="observedVariable" ref="A1:U2" insertRow="1" totalsRowShown="0" dataDxfId="131">
   <autoFilter ref="A1:U2" xr:uid="{0EDFDBC4-F33A-4222-BE29-11AF54DCA710}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="129"/>
-    <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="128"/>
-    <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="127"/>
-    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccession" dataDxfId="126"/>
-    <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="124"/>
-    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccession" dataDxfId="123"/>
-    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccession" dataDxfId="121"/>
-    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccession" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccession" dataDxfId="118"/>
-    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="117"/>
-    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="116"/>
-    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="115"/>
-    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccession" dataDxfId="114"/>
-    <tableColumn id="19" xr3:uid="{EE91A801-8376-4314-ADFB-6E32C3AE8AE4}" name="timeScale" dataDxfId="113"/>
-    <tableColumn id="22" xr3:uid="{A52D8785-E3B2-4548-AA8A-0964285F0DB9}" name="participant" dataDxfId="112"/>
-    <tableColumn id="21" xr3:uid="{CA21FA4C-5A61-4852-9BA7-6FDDF22D4ADC}" name="participantAccession" dataDxfId="111"/>
-    <tableColumn id="20" xr3:uid="{3DF54E16-A553-4C7E-9762-C6517F5AD994}" name="participantRole" dataDxfId="110"/>
-    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="participantRoleAccession" dataDxfId="109"/>
+    <tableColumn id="1" xr3:uid="{52AF96AA-DC3C-4AE1-9B73-089CA835EB6D}" name="studyId" dataDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{6323306B-E13C-4F7B-86EE-23DC8D1F262D}" name="variableId" dataDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{DAD62536-0510-4DD9-9444-8EBA12087E02}" name="variableName" dataDxfId="128"/>
+    <tableColumn id="4" xr3:uid="{FD87E241-A1C6-4BF6-81FC-38FE779F31D6}" name="variableAccession" dataDxfId="127"/>
+    <tableColumn id="5" xr3:uid="{ED4E4010-EAC9-4FB0-9577-906D949DB6BF}" name="traitName" dataDxfId="126"/>
+    <tableColumn id="6" xr3:uid="{DA4A34B4-67B2-4ABC-9FA6-0EBFB54B964D}" name="traitEntity" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{9A164C4C-E33C-4F52-9CA0-56F6EC009A34}" name="traitEntityAccession" dataDxfId="124"/>
+    <tableColumn id="8" xr3:uid="{FB4A5310-40B1-46EF-B98F-2CA2AC87CE59}" name="traitCharacteristic" dataDxfId="123"/>
+    <tableColumn id="9" xr3:uid="{59E17836-2938-469A-A999-F34CBAA00B67}" name="traitCharacteristicAccession" dataDxfId="122"/>
+    <tableColumn id="10" xr3:uid="{7F9E3661-278E-45F4-A718-37C7F238C752}" name="traitAccession" dataDxfId="121"/>
+    <tableColumn id="11" xr3:uid="{F49AEE2B-9512-4C72-A2BF-C945026C81A0}" name="methodName" dataDxfId="120"/>
+    <tableColumn id="12" xr3:uid="{8099D3A2-60AE-4466-B82A-EEC20FC58B7B}" name="methodAccession" dataDxfId="119"/>
+    <tableColumn id="13" xr3:uid="{6291B064-7EBD-42CC-B89D-568748A16FA5}" name="methodDesc" dataDxfId="118"/>
+    <tableColumn id="14" xr3:uid="{A01FDF2D-88FC-405F-BF1E-14B20EABB5B5}" name="methodRef" dataDxfId="117"/>
+    <tableColumn id="15" xr3:uid="{A15211C8-293C-4DE6-87B9-CF94F470AE75}" name="scaleName" dataDxfId="116"/>
+    <tableColumn id="16" xr3:uid="{648CBC04-7A14-4F7F-A7AF-D119B1714850}" name="scaleAccession" dataDxfId="115"/>
+    <tableColumn id="19" xr3:uid="{EE91A801-8376-4314-ADFB-6E32C3AE8AE4}" name="timeScale" dataDxfId="114"/>
+    <tableColumn id="22" xr3:uid="{A52D8785-E3B2-4548-AA8A-0964285F0DB9}" name="participant" dataDxfId="113"/>
+    <tableColumn id="21" xr3:uid="{CA21FA4C-5A61-4852-9BA7-6FDDF22D4ADC}" name="participantAccession" dataDxfId="112"/>
+    <tableColumn id="20" xr3:uid="{3DF54E16-A553-4C7E-9762-C6517F5AD994}" name="participantRole" dataDxfId="111"/>
+    <tableColumn id="17" xr3:uid="{AD46E78F-5D35-4B20-9822-0B2F83C5680D}" name="participantRoleAccession" dataDxfId="110"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}" name="environmentParameters" displayName="environmentParameters" ref="A1:C3" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}" name="environmentParameters" displayName="environmentParameters" ref="A1:C3" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="A1:C3" xr:uid="{AB1F2FD5-EB26-42FD-AA78-B5395A6174BE}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{5E761B2A-3F92-4181-AF5D-F423F0564A09}" name="envParam"/>
@@ -5598,119 +5621,120 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:T3" totalsRowShown="0" dataDxfId="98">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}" name="study" displayName="study" ref="A1:T3" totalsRowShown="0" dataDxfId="99">
   <autoFilter ref="A1:T3" xr:uid="{5E227E83-2F05-4244-925F-48F9556390CD}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="97"/>
-    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="sourceStudyId" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="94"/>
-    <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="93"/>
-    <tableColumn id="5" xr3:uid="{E557DB42-3379-4598-AAF9-21798BC64DAB}" name="studyEndDate" dataDxfId="92"/>
-    <tableColumn id="6" xr3:uid="{1EEA2EC5-CA19-40B4-9DFB-2DE9A9E916EA}" name="contactInst" dataDxfId="91"/>
-    <tableColumn id="7" xr3:uid="{E0A5C222-CFE5-4E9C-8E84-0892043DBD21}" name="locationCountry" dataDxfId="90"/>
-    <tableColumn id="8" xr3:uid="{7B635D2A-56C5-48B0-A880-E33ADE030AB1}" name="siteName" dataDxfId="89"/>
-    <tableColumn id="9" xr3:uid="{2F8227C3-F11C-4DAA-93EB-CEBD94FF81A9}" name="locationLatitude" dataDxfId="88"/>
-    <tableColumn id="10" xr3:uid="{6A14EB46-0BF4-45C6-9048-E1B7D13E633A}" name="locationLongitude" dataDxfId="87"/>
-    <tableColumn id="11" xr3:uid="{9954429A-AA41-408C-BB04-D73EDB89D73F}" name="locationAltitude" dataDxfId="86"/>
-    <tableColumn id="12" xr3:uid="{39FEDA43-D994-4742-B319-3DFED43EF79B}" name="expeDesignDesc" dataDxfId="85"/>
-    <tableColumn id="13" xr3:uid="{C9F6A881-1CF1-4AD9-8305-B7E26FD78E3B}" name="expeDesignType" dataDxfId="84"/>
-    <tableColumn id="14" xr3:uid="{253A58C7-1A2A-4D25-9622-3AE33F89A685}" name="obsUnitLevelHierarchy" dataDxfId="83"/>
-    <tableColumn id="15" xr3:uid="{10DCEB5F-0BF5-4476-83E5-B973A516A8CD}" name="obsUnitDesc" dataDxfId="82"/>
-    <tableColumn id="16" xr3:uid="{0D36E7FE-2245-4B79-9A59-4C64590731A5}" name="growthFacilityDesc" dataDxfId="81"/>
-    <tableColumn id="17" xr3:uid="{599307E8-6E88-4D3F-BF48-ADF70D109D18}" name="growthFacilityType" dataDxfId="80"/>
-    <tableColumn id="18" xr3:uid="{63403E81-283C-4E2E-984D-9EFC0886E90C}" name="culturalPractice" dataDxfId="79"/>
-    <tableColumn id="19" xr3:uid="{E74D4B3A-67BC-482F-8485-FC7D9088A8B6}" name="expeDesignMap" dataDxfId="78"/>
+    <tableColumn id="1" xr3:uid="{EE95CF2F-813E-4690-97C4-79C304F65B9C}" name="studyId" dataDxfId="98"/>
+    <tableColumn id="20" xr3:uid="{B540CC62-E9C4-45D9-ADBE-8B9EAB4D0769}" name="sourceStudyId" dataDxfId="97"/>
+    <tableColumn id="2" xr3:uid="{799EAD4E-60F7-47E4-B3B2-8BD859F0673D}" name="studyTitle" dataDxfId="96"/>
+    <tableColumn id="3" xr3:uid="{A2063A94-CC8E-425D-A71D-C0EDE3148180}" name="studyDescription" dataDxfId="95"/>
+    <tableColumn id="4" xr3:uid="{4DCF1664-298B-4E1C-8B80-483A31FB0BDB}" name="studyStartDate" dataDxfId="94"/>
+    <tableColumn id="5" xr3:uid="{E557DB42-3379-4598-AAF9-21798BC64DAB}" name="studyEndDate" dataDxfId="93"/>
+    <tableColumn id="6" xr3:uid="{1EEA2EC5-CA19-40B4-9DFB-2DE9A9E916EA}" name="contactInst" dataDxfId="92"/>
+    <tableColumn id="7" xr3:uid="{E0A5C222-CFE5-4E9C-8E84-0892043DBD21}" name="locationCountry" dataDxfId="91"/>
+    <tableColumn id="8" xr3:uid="{7B635D2A-56C5-48B0-A880-E33ADE030AB1}" name="siteName" dataDxfId="90"/>
+    <tableColumn id="9" xr3:uid="{2F8227C3-F11C-4DAA-93EB-CEBD94FF81A9}" name="locationLatitude" dataDxfId="89"/>
+    <tableColumn id="10" xr3:uid="{6A14EB46-0BF4-45C6-9048-E1B7D13E633A}" name="locationLongitude" dataDxfId="88"/>
+    <tableColumn id="11" xr3:uid="{9954429A-AA41-408C-BB04-D73EDB89D73F}" name="locationAltitude" dataDxfId="87"/>
+    <tableColumn id="12" xr3:uid="{39FEDA43-D994-4742-B319-3DFED43EF79B}" name="expeDesignDesc" dataDxfId="86"/>
+    <tableColumn id="13" xr3:uid="{C9F6A881-1CF1-4AD9-8305-B7E26FD78E3B}" name="expeDesignType" dataDxfId="85"/>
+    <tableColumn id="14" xr3:uid="{253A58C7-1A2A-4D25-9622-3AE33F89A685}" name="obsUnitLevelHierarchy" dataDxfId="84"/>
+    <tableColumn id="15" xr3:uid="{10DCEB5F-0BF5-4476-83E5-B973A516A8CD}" name="obsUnitDesc" dataDxfId="83"/>
+    <tableColumn id="16" xr3:uid="{0D36E7FE-2245-4B79-9A59-4C64590731A5}" name="growthFacilityDesc" dataDxfId="82"/>
+    <tableColumn id="17" xr3:uid="{599307E8-6E88-4D3F-BF48-ADF70D109D18}" name="growthFacilityType" dataDxfId="81"/>
+    <tableColumn id="18" xr3:uid="{63403E81-283C-4E2E-984D-9EFC0886E90C}" name="culturalPractice" dataDxfId="80"/>
+    <tableColumn id="19" xr3:uid="{E74D4B3A-67BC-482F-8485-FC7D9088A8B6}" name="expeDesignMap" dataDxfId="79"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}" name="person" displayName="person" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="77" dataDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}" name="person" displayName="person" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="78" dataDxfId="77">
   <autoFilter ref="A1:F2" xr:uid="{2FBCF0B0-7AB0-436F-9431-67BEDDE78EB3}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{49A703DB-336A-4F60-9DA6-8249763A2765}" name="studyId" dataDxfId="75"/>
-    <tableColumn id="2" xr3:uid="{65039BF4-A122-4B88-8EB2-FD3ED61B8912}" name="personName" dataDxfId="74"/>
-    <tableColumn id="3" xr3:uid="{4B7588A4-B756-4E28-B8A4-AFB8D62031B4}" name="personEmail" dataDxfId="73"/>
-    <tableColumn id="4" xr3:uid="{639FC837-B543-4A62-B2C2-3EE761EF5EF7}" name="personId" dataDxfId="72"/>
-    <tableColumn id="5" xr3:uid="{593F31A8-CDAA-47CF-89F3-2902C6B8D3C8}" name="personRole" dataDxfId="71"/>
-    <tableColumn id="6" xr3:uid="{5FCF059F-31D5-4218-8D81-DC379C42EAF4}" name="personAffiliation" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{49A703DB-336A-4F60-9DA6-8249763A2765}" name="studyId" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{65039BF4-A122-4B88-8EB2-FD3ED61B8912}" name="personName" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{4B7588A4-B756-4E28-B8A4-AFB8D62031B4}" name="personEmail" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{639FC837-B543-4A62-B2C2-3EE761EF5EF7}" name="personId" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{593F31A8-CDAA-47CF-89F3-2902C6B8D3C8}" name="personRole" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{5FCF059F-31D5-4218-8D81-DC379C42EAF4}" name="personAffiliation" dataDxfId="71"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}" name="dataFile" displayName="dataFile" ref="A1:D2" insertRow="1" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
-  <autoFilter ref="A1:D2" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AD6A7B95-2E4C-4264-86B4-35031C8932E3}" name="studyId" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{A5C92CF7-B78F-4910-A250-8A16D6E7889C}" name="dataFileLink" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{620AC217-74DA-496A-9696-16EF7D98E86C}" name="dataFileDesc" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{79F128D7-FDA0-4F62-B04B-DAEE7E495850}" name="dataFileVersion" dataDxfId="64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}" name="dataFile" displayName="dataFile" ref="A1:E2" insertRow="1" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69">
+  <autoFilter ref="A1:E2" xr:uid="{6A3BD8AE-973B-42AE-B791-86C37DE5452E}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{AD6A7B95-2E4C-4264-86B4-35031C8932E3}" name="studyId" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{A5C92CF7-B78F-4910-A250-8A16D6E7889C}" name="dataFileLink" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{620AC217-74DA-496A-9696-16EF7D98E86C}" name="dataFileDesc" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{AFC6BCDB-79B5-4940-A3BB-0EEC9F1306A5}" name="dataFileType" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{79F128D7-FDA0-4F62-B04B-DAEE7E495850}" name="dataFileVersion" dataDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}" name="biologicalMaterial" displayName="biologicalMaterial" ref="A1:X2" insertRow="1" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}" name="biologicalMaterial" displayName="biologicalMaterial" ref="A1:X2" insertRow="1" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
   <autoFilter ref="A1:X2" xr:uid="{CD8645E7-2CD1-4841-84CC-19654A603435}"/>
   <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{71E6992E-3AF7-4C8A-9C1E-930C105005E2}" name="studyId" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{BA8B45A2-9F79-4EE6-A38F-EF56D5CE4A1A}" name="biologicalMaterialId" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{546FEA19-FA9D-47D3-BF6E-57CDA029B0A3}" name="biologicalMaterialExtId" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{0DD21880-A5E2-4076-AA9F-554DE7C7E0D1}" name="organism" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{9760C8F1-7162-4A84-80C2-FBEC779AFAD0}" name="genus" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{D7026284-DE40-4B04-A583-983A0B5FB5BB}" name="species" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{22046373-BBD5-4919-AC4C-AA8E91D97026}" name="infraspecificName" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{579B0DCA-BD9C-4E7B-BB3B-3FB19A4CBCA3}" name="biologicalMaterialLatitude" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{A7E064AC-CDCF-4898-BEF3-07CF88887A4E}" name="biologicalMaterialLongitude" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{D55DD07C-0BE6-4D7D-80E1-B7195245711A}" name="biologicalMaterialAltitude" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{CA82A017-8E46-417C-9A1F-D7010C7B489F}" name="biologicalMaterialCoordUncertainty" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{16F6B082-1241-4094-AFDC-6E6F5B63F502}" name="biologicalMaterialPreprocessing" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{16F5564F-9F1B-4CEB-8DEC-4F46E89C2EB5}" name="materialSourceId" dataDxfId="49"/>
-    <tableColumn id="14" xr3:uid="{0AB5DA63-1709-41B8-9FAD-5B1A8A45E649}" name="materialSourceDoi" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{26116E4A-CA0A-4D6C-A863-AEA24B0E0C24}" name="materialSourceAccNumber" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{0C2E647E-5127-470F-859E-ED727EEFA3B9}" name="materialSourceAccName" dataDxfId="46"/>
-    <tableColumn id="17" xr3:uid="{B6097563-29EF-4C10-9096-04A2C164B15A}" name="materialSourceInstCode" dataDxfId="45"/>
-    <tableColumn id="18" xr3:uid="{BEA38246-EAA3-4450-B29F-D608607C2513}" name="materialSourceInstName" dataDxfId="44"/>
-    <tableColumn id="19" xr3:uid="{E8257013-CD5D-4534-9CD0-08D9EBBE7EF0}" name="materialSourceOtherIds" dataDxfId="43"/>
-    <tableColumn id="20" xr3:uid="{BE0E6D94-2ED0-4863-9DE5-9AA6BD4643D6}" name="materialSourceLatitude" dataDxfId="42"/>
-    <tableColumn id="21" xr3:uid="{BD849876-C99C-4475-87D4-DEECBE575F67}" name="materialSourceLongitude" dataDxfId="41"/>
-    <tableColumn id="22" xr3:uid="{0C871681-B897-43DD-A6BE-F03CAA6574F6}" name="materialSourceAltitude" dataDxfId="40"/>
-    <tableColumn id="23" xr3:uid="{ECC67BD8-3E1F-4A97-95B0-A9CCE07839CA}" name="materialSourceCoordUncertainty" dataDxfId="39"/>
-    <tableColumn id="24" xr3:uid="{C66E78D2-DB97-4D59-8D52-ECE79ED6BB86}" name="materialSourceDesc" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{71E6992E-3AF7-4C8A-9C1E-930C105005E2}" name="studyId" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{BA8B45A2-9F79-4EE6-A38F-EF56D5CE4A1A}" name="biologicalMaterialId" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{546FEA19-FA9D-47D3-BF6E-57CDA029B0A3}" name="biologicalMaterialExtId" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{0DD21880-A5E2-4076-AA9F-554DE7C7E0D1}" name="organism" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{9760C8F1-7162-4A84-80C2-FBEC779AFAD0}" name="genus" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{D7026284-DE40-4B04-A583-983A0B5FB5BB}" name="species" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{22046373-BBD5-4919-AC4C-AA8E91D97026}" name="infraspecificName" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{579B0DCA-BD9C-4E7B-BB3B-3FB19A4CBCA3}" name="biologicalMaterialLatitude" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{A7E064AC-CDCF-4898-BEF3-07CF88887A4E}" name="biologicalMaterialLongitude" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{D55DD07C-0BE6-4D7D-80E1-B7195245711A}" name="biologicalMaterialAltitude" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{CA82A017-8E46-417C-9A1F-D7010C7B489F}" name="biologicalMaterialCoordUncertainty" dataDxfId="52"/>
+    <tableColumn id="12" xr3:uid="{16F6B082-1241-4094-AFDC-6E6F5B63F502}" name="biologicalMaterialPreprocessing" dataDxfId="51"/>
+    <tableColumn id="13" xr3:uid="{16F5564F-9F1B-4CEB-8DEC-4F46E89C2EB5}" name="materialSourceId" dataDxfId="50"/>
+    <tableColumn id="14" xr3:uid="{0AB5DA63-1709-41B8-9FAD-5B1A8A45E649}" name="materialSourceDoi" dataDxfId="49"/>
+    <tableColumn id="15" xr3:uid="{26116E4A-CA0A-4D6C-A863-AEA24B0E0C24}" name="materialSourceAccNumber" dataDxfId="48"/>
+    <tableColumn id="16" xr3:uid="{0C2E647E-5127-470F-859E-ED727EEFA3B9}" name="materialSourceAccName" dataDxfId="47"/>
+    <tableColumn id="17" xr3:uid="{B6097563-29EF-4C10-9096-04A2C164B15A}" name="materialSourceInstCode" dataDxfId="46"/>
+    <tableColumn id="18" xr3:uid="{BEA38246-EAA3-4450-B29F-D608607C2513}" name="materialSourceInstName" dataDxfId="45"/>
+    <tableColumn id="19" xr3:uid="{E8257013-CD5D-4534-9CD0-08D9EBBE7EF0}" name="materialSourceOtherIds" dataDxfId="44"/>
+    <tableColumn id="20" xr3:uid="{BE0E6D94-2ED0-4863-9DE5-9AA6BD4643D6}" name="materialSourceLatitude" dataDxfId="43"/>
+    <tableColumn id="21" xr3:uid="{BD849876-C99C-4475-87D4-DEECBE575F67}" name="materialSourceLongitude" dataDxfId="42"/>
+    <tableColumn id="22" xr3:uid="{0C871681-B897-43DD-A6BE-F03CAA6574F6}" name="materialSourceAltitude" dataDxfId="41"/>
+    <tableColumn id="23" xr3:uid="{ECC67BD8-3E1F-4A97-95B0-A9CCE07839CA}" name="materialSourceCoordUncertainty" dataDxfId="40"/>
+    <tableColumn id="24" xr3:uid="{C66E78D2-DB97-4D59-8D52-ECE79ED6BB86}" name="materialSourceDesc" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}" name="environment" displayName="environment" ref="A1:C2" insertRow="1" totalsRowShown="0" headerRowDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}" name="environment" displayName="environment" ref="A1:C2" insertRow="1" totalsRowShown="0" headerRowDxfId="38">
   <autoFilter ref="A1:C2" xr:uid="{1C4F81EC-6E53-43AA-B6CF-9BA631481909}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{08C0BD82-D970-44E6-99E3-B4872FECEFE5}" name="studyId" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{F9DC7CC5-88B3-4A9A-B462-9FB971836B81}" name="envParam" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{65E72A00-3C03-4A17-922C-EE6A4A3D8D80}" name="envParamValue" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{08C0BD82-D970-44E6-99E3-B4872FECEFE5}" name="studyId" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{F9DC7CC5-88B3-4A9A-B462-9FB971836B81}" name="envParam" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{65E72A00-3C03-4A17-922C-EE6A4A3D8D80}" name="envParamValue" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}" name="experimentalFactor" displayName="experimentalFactor" ref="A1:F2" totalsRowShown="0" headerRowDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}" name="experimentalFactor" displayName="experimentalFactor" ref="A1:F2" totalsRowShown="0" headerRowDxfId="34">
   <autoFilter ref="A1:F2" xr:uid="{9DB56221-E63F-405B-979B-FD6B29D3B9AE}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{8AF0BF35-BAC4-4E9A-A1CC-B83DC7399496}" name="expeFactorCode" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{67BFB12E-F4AF-4C45-B7B6-4791A656C30A}" name="expeFactorId" dataDxfId="30">
+    <tableColumn id="1" xr3:uid="{8033D24B-35FE-4753-9513-1BA7E8E27122}" name="studyId" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{8AF0BF35-BAC4-4E9A-A1CC-B83DC7399496}" name="expeFactorCode" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{67BFB12E-F4AF-4C45-B7B6-4791A656C30A}" name="expeFactorId" dataDxfId="31">
       <calculatedColumnFormula>CONCATENATE(experimentalFactor[studyId],"-",experimentalFactor[expeFactorCode])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{0E59C639-24C1-40B6-85BF-F9DA37B289AF}" name="expeFactorType" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{45088180-C6C0-4340-B527-76C01394AC82}" name="expeFactorDesc" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{79953CF7-2E96-4871-AAED-69F19C77A395}" name="expeFactorValues" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5733,16 +5757,16 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:G2" totalsRowShown="0" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}" name="event" displayName="event" ref="A1:G2" totalsRowShown="0" dataDxfId="27">
   <autoFilter ref="A1:G2" xr:uid="{E52243D7-2662-4692-B203-793CCE48631D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{DB25986C-BD6F-40F9-A226-C9A11BBDF460}" name="studyId" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{6EE72788-DEAD-4FC0-9383-C6415EC5E8A5}" name="obsUnitId" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{59210F7A-BDE1-4221-BA01-D09327E85900}" name="expeFactorLevelId" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{0DDCD5FF-AC45-4794-9B28-BBD982C1FB84}" name="eventType" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{DB25986C-BD6F-40F9-A226-C9A11BBDF460}" name="studyId" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{6EE72788-DEAD-4FC0-9383-C6415EC5E8A5}" name="obsUnitId" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{59210F7A-BDE1-4221-BA01-D09327E85900}" name="expeFactorLevelId" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{0DDCD5FF-AC45-4794-9B28-BBD982C1FB84}" name="eventType" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{F8E58477-EC1C-4F97-B99C-B939249E19E9}" name="eventAccNumber" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{E826B0E9-8F41-4E58-9D61-690A1F38823F}" name="eventDesc" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{6ABA4348-63AB-41DB-837E-5BE18C09264B}" name="eventDate" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="MiappeStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21906,15 +21930,14 @@
   <sheetPr>
     <tabColor rgb="FF008000"/>
   </sheetPr>
-  <dimension ref="A1:X997"/>
+  <dimension ref="A1:Y997"/>
   <sheetFormatPr defaultColWidth="14.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="20.42578125" customWidth="1"/>
-    <col min="16383" max="16383" width="11.42578125" customWidth="1"/>
-    <col min="16384" max="16384" width="11.5703125" customWidth="1"/>
+    <col min="1" max="5" width="20.42578125" customWidth="1"/>
+    <col min="16384" max="16384" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
         <v>66</v>
       </c>
@@ -21925,9 +21948,11 @@
         <v>160</v>
       </c>
       <c r="D1" s="52" t="s">
+        <v>703</v>
+      </c>
+      <c r="E1" s="52" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="36"/>
       <c r="F1" s="36"/>
       <c r="G1" s="36"/>
       <c r="H1" s="36"/>
@@ -21947,57 +21972,65 @@
       <c r="V1" s="36"/>
       <c r="W1" s="36"/>
       <c r="X1" s="36"/>
-    </row>
-    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y1" s="36"/>
+    </row>
+    <row r="2" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="E2" s="13"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-    </row>
-    <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
-    </row>
-    <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-    </row>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
-    </row>
-    <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
